--- a/public/material-upload-template.xlsx
+++ b/public/material-upload-template.xlsx
@@ -2,8 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上傳資料" sheetId="1" r:id="Ra3027fe167de48a9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分工與欄位說明" sheetId="2" r:id="Rc355b70a16d04a16"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上傳資料" sheetId="1" r:id="R3e7c563ac3fa4ea7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -19,7 +18,7 @@
     <x:numFmt numFmtId="201" formatCode="0"/>
     <x:numFmt numFmtId="202" formatCode="General"/>
   </x:numFmts>
-  <x:fonts count="6">
+  <x:fonts count="5">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -44,12 +43,6 @@
       <x:b/>
       <x:sz val="11"/>
       <x:color rgb="FFFFFFFF"/>
-      <x:name val="Arial"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="11"/>
-      <x:color rgb="FF242B33"/>
       <x:name val="Arial"/>
     </x:font>
   </x:fonts>
@@ -160,7 +153,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="59">
+  <x:cellXfs count="45">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -289,48 +282,6 @@
     </x:xf>
     <x:xf numFmtId="202" fontId="1" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="1" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -560,7 +511,7 @@
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
       <x:c r="A1" s="5" t="str">
-        <x:v>CE BOM 空白交付範本</x:v>
+        <x:v>CE BOM 交付格式</x:v>
       </x:c>
       <x:c r="B1" s="6"/>
       <x:c r="C1" s="6"/>
@@ -583,7 +534,7 @@
     </x:row>
     <x:row r="2" ht="27" customHeight="1">
       <x:c r="A2" s="7" t="str">
-        <x:v>規格日期 2026-10-21。第 4 列為固定表頭，第 5 列起填資料；請先閱讀「分工與欄位說明」。</x:v>
+        <x:v>第4列表頭請保留，第5列起填寫資料</x:v>
       </x:c>
       <x:c r="B2" s="3"/>
       <x:c r="C2" s="3"/>
@@ -604,77 +555,26 @@
       <x:c r="R2" s="3"/>
       <x:c r="S2" s="3"/>
     </x:row>
-    <x:row r="3" ht="36" customHeight="1">
-      <x:c r="A3" s="11" t="str">
-        <x:v>RD 原始
-CE 保留</x:v>
-      </x:c>
-      <x:c r="B3" s="11" t="str">
-        <x:v>RD 原始
-CE 保留</x:v>
-      </x:c>
-      <x:c r="C3" s="11" t="str">
-        <x:v>RD 原始
-CE 保留</x:v>
-      </x:c>
-      <x:c r="D3" s="11" t="str">
-        <x:v>RD 原始
-CE 保留</x:v>
-      </x:c>
-      <x:c r="E3" s="11" t="str">
-        <x:v>RD 提供
-CE 核對</x:v>
-      </x:c>
-      <x:c r="F3" s="11" t="str">
-        <x:v>CE 保留舊格式</x:v>
-      </x:c>
-      <x:c r="G3" s="11" t="str">
-        <x:v>CE 核對
-帶出</x:v>
-      </x:c>
-      <x:c r="H3" s="11" t="str">
-        <x:v>CE 從來源帶出</x:v>
-      </x:c>
-      <x:c r="I3" s="11" t="str">
-        <x:v>CE 從來源帶出</x:v>
-      </x:c>
-      <x:c r="J3" s="11" t="str">
-        <x:v>CE 從來源帶出</x:v>
-      </x:c>
-      <x:c r="K3" s="11" t="str">
-        <x:v>原始分組
-CE 保留</x:v>
-      </x:c>
-      <x:c r="L3" s="11" t="str">
-        <x:v>來源資料
-CE 保留</x:v>
-      </x:c>
-      <x:c r="M3" s="11" t="str">
-        <x:v>來源參考
-CE 保留</x:v>
-      </x:c>
-      <x:c r="N3" s="11" t="str">
-        <x:v>CE 從公司系統帶出</x:v>
-      </x:c>
-      <x:c r="O3" s="11" t="str">
-        <x:v>CE 從公司系統帶出</x:v>
-      </x:c>
-      <x:c r="P3" s="11" t="str">
-        <x:v>RD 原始
-CE 保留</x:v>
-      </x:c>
-      <x:c r="Q3" s="11" t="str">
-        <x:v>RD 原始
-CE 保留</x:v>
-      </x:c>
-      <x:c r="R3" s="11" t="str">
-        <x:v>RD 原始
-CE 保留</x:v>
-      </x:c>
-      <x:c r="S3" s="12" t="str">
-        <x:v>CE 補欄
-帶出原文</x:v>
-      </x:c>
+    <x:row r="3" ht="10" customHeight="1">
+      <x:c r="A3" s="1"/>
+      <x:c r="B3" s="1"/>
+      <x:c r="C3" s="1"/>
+      <x:c r="D3" s="1"/>
+      <x:c r="E3" s="1"/>
+      <x:c r="F3" s="1"/>
+      <x:c r="G3" s="1"/>
+      <x:c r="H3" s="1"/>
+      <x:c r="I3" s="1"/>
+      <x:c r="J3" s="1"/>
+      <x:c r="K3" s="1"/>
+      <x:c r="L3" s="1"/>
+      <x:c r="M3" s="1"/>
+      <x:c r="N3" s="1"/>
+      <x:c r="O3" s="1"/>
+      <x:c r="P3" s="1"/>
+      <x:c r="Q3" s="1"/>
+      <x:c r="R3" s="1"/>
+      <x:c r="S3" s="1"/>
     </x:row>
     <x:row r="4" ht="42" customHeight="1">
       <x:c r="A4" s="21" t="str">
@@ -1368,620 +1268,4 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetPr>
-    <x:tabColor rgb="FF888D93"/>
-  </x:sheetPr>
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="30" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="76" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="27" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="40" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="5" t="str">
-        <x:v>CE BOM 交付分工與欄位說明</x:v>
-      </x:c>
-      <x:c r="B1" s="6"/>
-      <x:c r="C1" s="6"/>
-      <x:c r="D1" s="6"/>
-      <x:c r="E1" s="6"/>
-    </x:row>
-    <x:row r="2" ht="25" customHeight="1">
-      <x:c r="A2" s="7" t="str">
-        <x:v>規格日期 2026-10-21</x:v>
-      </x:c>
-      <x:c r="B2" s="3"/>
-      <x:c r="C2" s="3"/>
-      <x:c r="D2" s="3"/>
-      <x:c r="E2" s="3"/>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="3"/>
-      <x:c r="B3" s="3"/>
-      <x:c r="C3" s="3"/>
-      <x:c r="D3" s="3"/>
-      <x:c r="E3" s="3"/>
-    </x:row>
-    <x:row r="4" ht="27" customHeight="1">
-      <x:c r="A4" s="45" t="str">
-        <x:v>一、作業分工</x:v>
-      </x:c>
-      <x:c r="B4" s="8"/>
-      <x:c r="C4" s="8"/>
-      <x:c r="D4" s="8"/>
-      <x:c r="E4" s="8"/>
-    </x:row>
-    <x:row r="5" ht="28" customHeight="1">
-      <x:c r="A5" s="21" t="str">
-        <x:v>角色</x:v>
-      </x:c>
-      <x:c r="B5" s="22" t="str">
-        <x:v>交付結果</x:v>
-      </x:c>
-      <x:c r="C5" s="23" t="str">
-        <x:v>責任</x:v>
-      </x:c>
-      <x:c r="D5" s="3"/>
-      <x:c r="E5" s="3"/>
-    </x:row>
-    <x:row r="6" ht="48" customHeight="1">
-      <x:c r="A6" s="47" t="str">
-        <x:v>公司現有系統</x:v>
-      </x:c>
-      <x:c r="B6" s="47" t="str">
-        <x:v>公司料號與來源狀態</x:v>
-      </x:c>
-      <x:c r="C6" s="47" t="str">
-        <x:v>維持原本的料號、料況與申請／核准流程，是正式資料來源；本工具不要求修改公司系統。</x:v>
-      </x:c>
-      <x:c r="D6" s="3"/>
-      <x:c r="E6" s="3"/>
-    </x:row>
-    <x:row r="7" ht="48" customHeight="1">
-      <x:c r="A7" s="47" t="str">
-        <x:v>CE</x:v>
-      </x:c>
-      <x:c r="B7" s="47" t="str">
-        <x:v>整理後 BOM＋零件狀態</x:v>
-      </x:c>
-      <x:c r="C7" s="47" t="str">
-        <x:v>依 RD 提供的客戶 BOM，利用公司現有系統整理並轉出清單；保留設計欄位，補上右側「零件狀態」，再交回 RD。查無料號或狀態不明時明確註記待確認。</x:v>
-      </x:c>
-      <x:c r="D7" s="3"/>
-      <x:c r="E7" s="3"/>
-    </x:row>
-    <x:row r="8" ht="48" customHeight="1">
-      <x:c r="A8" s="47" t="str">
-        <x:v>料號追蹤工具</x:v>
-      </x:c>
-      <x:c r="B8" s="47" t="str">
-        <x:v>可檢查的料號總表與追蹤紀錄</x:v>
-      </x:c>
-      <x:c r="C8" s="47" t="str">
-        <x:v>自動讀取欄位、整理主料與替代料、對應 TX、呈現料號與風險；保留原文，不代替公司系統核准料號，也不替 RD 決定能否採用。</x:v>
-      </x:c>
-      <x:c r="D8" s="3"/>
-      <x:c r="E8" s="3"/>
-    </x:row>
-    <x:row r="9" ht="48" customHeight="1">
-      <x:c r="A9" s="47" t="str">
-        <x:v>RD</x:v>
-      </x:c>
-      <x:c r="B9" s="47" t="str">
-        <x:v>確認結果與後續申請追蹤</x:v>
-      </x:c>
-      <x:c r="C9" s="47" t="str">
-        <x:v>提供設計 BOM，匯入 CE 清單後核對位號、用量、料號與零件狀態；依公司流程確認選用／申請事項，再於網站記錄追蹤說明、單號與更新人。</x:v>
-      </x:c>
-      <x:c r="D9" s="3"/>
-      <x:c r="E9" s="3"/>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="3"/>
-      <x:c r="B10" s="3"/>
-      <x:c r="C10" s="3"/>
-      <x:c r="D10" s="3"/>
-      <x:c r="E10" s="3"/>
-    </x:row>
-    <x:row r="11" ht="27" customHeight="1">
-      <x:c r="A11" s="45" t="str">
-        <x:v>二、共同規則</x:v>
-      </x:c>
-      <x:c r="B11" s="8"/>
-      <x:c r="C11" s="8"/>
-      <x:c r="D11" s="8"/>
-      <x:c r="E11" s="8"/>
-    </x:row>
-    <x:row r="12" ht="44" customHeight="1">
-      <x:c r="A12" s="48" t="str">
-        <x:v>規則 1</x:v>
-      </x:c>
-      <x:c r="B12" s="48"/>
-      <x:c r="C12" s="47" t="str">
-        <x:v>CE 整理與帶出狀態，不代表 CE 有權變更所有來源狀態；禁用、EOL、ODM 不建議用料等設定仍依公司既有權責窗口處理。</x:v>
-      </x:c>
-      <x:c r="D12" s="48"/>
-      <x:c r="E12" s="48"/>
-    </x:row>
-    <x:row r="13" ht="44" customHeight="1">
-      <x:c r="A13" s="48" t="str">
-        <x:v>規則 2</x:v>
-      </x:c>
-      <x:c r="B13" s="48"/>
-      <x:c r="C13" s="47" t="str">
-        <x:v>Sourcing Status 是供應／核准來源狀態；零件狀態是新設計使用限制。兩欄分開保留。Approved／Active 不代表可以忽略禁用或 ODM 不建議用料。</x:v>
-      </x:c>
-      <x:c r="D13" s="48"/>
-      <x:c r="E13" s="48"/>
-    </x:row>
-    <x:row r="14" ht="44" customHeight="1">
-      <x:c r="A14" s="48" t="str">
-        <x:v>規則 3</x:v>
-      </x:c>
-      <x:c r="B14" s="48"/>
-      <x:c r="C14" s="47" t="str">
-        <x:v>零件狀態放在 BOM 最右側，由 CE 帶出公司原文；未確認時填待確認，不得自行改填 Approved 或可用。查無公司料號時，Part Number 保持空白。</x:v>
-      </x:c>
-      <x:c r="D14" s="48"/>
-      <x:c r="E14" s="48"/>
-    </x:row>
-    <x:row r="15" ht="44" customHeight="1">
-      <x:c r="A15" s="48" t="str">
-        <x:v>規則 4</x:v>
-      </x:c>
-      <x:c r="B15" s="48"/>
-      <x:c r="C15" s="47" t="str">
-        <x:v>料號追蹤、單號、EE 是 RD 在網站維護的作業紀錄，CE 不需為了交付清單額外填寫；零件狀態不會自動建立申請追蹤。</x:v>
-      </x:c>
-      <x:c r="D15" s="48"/>
-      <x:c r="E15" s="48"/>
-    </x:row>
-    <x:row r="16" ht="44" customHeight="1">
-      <x:c r="A16" s="48" t="str">
-        <x:v>規則 5</x:v>
-      </x:c>
-      <x:c r="B16" s="48"/>
-      <x:c r="C16" s="47" t="str">
-        <x:v>範例中的料號、廠商與狀態都是格式示範，不能當成真實選料、核准或替代料相容性依據。</x:v>
-      </x:c>
-      <x:c r="D16" s="48"/>
-      <x:c r="E16" s="48"/>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" s="3"/>
-      <x:c r="B17" s="3"/>
-      <x:c r="C17" s="3"/>
-      <x:c r="D17" s="3"/>
-      <x:c r="E17" s="3"/>
-    </x:row>
-    <x:row r="18" ht="27" customHeight="1">
-      <x:c r="A18" s="45" t="str">
-        <x:v>三、交付與匯入步驟</x:v>
-      </x:c>
-      <x:c r="B18" s="8"/>
-      <x:c r="C18" s="8"/>
-      <x:c r="D18" s="8"/>
-      <x:c r="E18" s="8"/>
-    </x:row>
-    <x:row r="19" ht="44" customHeight="1">
-      <x:c r="A19" s="48" t="str">
-        <x:v>步驟 1</x:v>
-      </x:c>
-      <x:c r="B19" s="48"/>
-      <x:c r="C19" s="47" t="str">
-        <x:v>RD 提供單一專案／版本的客戶 BOM，CE 保留設計料名、位號、用量與圖面資料。</x:v>
-      </x:c>
-      <x:c r="D19" s="48"/>
-      <x:c r="E19" s="48"/>
-    </x:row>
-    <x:row r="20" ht="44" customHeight="1">
-      <x:c r="A20" s="48" t="str">
-        <x:v>步驟 2</x:v>
-      </x:c>
-      <x:c r="B20" s="48"/>
-      <x:c r="C20" s="47" t="str">
-        <x:v>CE 利用公司現有系統核對並帶出公司料號、供應狀態等資料，在最右側補上零件狀態；未知處明確填待確認。</x:v>
-      </x:c>
-      <x:c r="D20" s="48"/>
-      <x:c r="E20" s="48"/>
-    </x:row>
-    <x:row r="21" ht="44" customHeight="1">
-      <x:c r="A21" s="48" t="str">
-        <x:v>步驟 3</x:v>
-      </x:c>
-      <x:c r="B21" s="48"/>
-      <x:c r="C21" s="47" t="str">
-        <x:v>CE 依空白範本的固定表頭交付 Excel；一列一個廠商料，同組替代料相鄰排列，保留 Ref_tmp／Ref Des。</x:v>
-      </x:c>
-      <x:c r="D21" s="48"/>
-      <x:c r="E21" s="48"/>
-    </x:row>
-    <x:row r="22" ht="44" customHeight="1">
-      <x:c r="A22" s="48" t="str">
-        <x:v>步驟 4</x:v>
-      </x:c>
-      <x:c r="B22" s="48"/>
-      <x:c r="C22" s="47" t="str">
-        <x:v>RD 使用上傳 BOM 匯入，核對群組數、位號、MPN、公司料號、供應狀態與零件狀態。工具只整理與提示，不自動核准。</x:v>
-      </x:c>
-      <x:c r="D22" s="48"/>
-      <x:c r="E22" s="48"/>
-    </x:row>
-    <x:row r="23" ht="44" customHeight="1">
-      <x:c r="A23" s="48" t="str">
-        <x:v>步驟 5</x:v>
-      </x:c>
-      <x:c r="B23" s="48"/>
-      <x:c r="C23" s="47" t="str">
-        <x:v>RD 依公司流程處理選用與申請；料號追蹤、單號、EE 與圖片於網站維護，再匯出結果供確認。</x:v>
-      </x:c>
-      <x:c r="D23" s="48"/>
-      <x:c r="E23" s="48"/>
-    </x:row>
-    <x:row r="24">
-      <x:c r="A24" s="3"/>
-      <x:c r="B24" s="3"/>
-      <x:c r="C24" s="3"/>
-      <x:c r="D24" s="3"/>
-      <x:c r="E24" s="3"/>
-    </x:row>
-    <x:row r="25" ht="27" customHeight="1">
-      <x:c r="A25" s="45" t="str">
-        <x:v>四、固定欄位與責任</x:v>
-      </x:c>
-      <x:c r="B25" s="8"/>
-      <x:c r="C25" s="8"/>
-      <x:c r="D25" s="8"/>
-      <x:c r="E25" s="8"/>
-    </x:row>
-    <x:row r="26" ht="35" customHeight="1">
-      <x:c r="A26" s="21" t="str">
-        <x:v>Excel 表頭（第 4 列）</x:v>
-      </x:c>
-      <x:c r="B26" s="22" t="str">
-        <x:v>欄位責任</x:v>
-      </x:c>
-      <x:c r="C26" s="22" t="str">
-        <x:v>填寫要求</x:v>
-      </x:c>
-      <x:c r="D26" s="22" t="str">
-        <x:v>匯入位置</x:v>
-      </x:c>
-      <x:c r="E26" s="23" t="str">
-        <x:v>格式示例（DEMO）</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" ht="34" customHeight="1">
-      <x:c r="A27" s="50" t="str">
-        <x:v>Level</x:v>
-      </x:c>
-      <x:c r="B27" s="50" t="str">
-        <x:v>RD 原始／CE 保留</x:v>
-      </x:c>
-      <x:c r="C27" s="51" t="str">
-        <x:v>料件列填 2；0 為系統、1 為模組，網站只建立 Level 2 料件。</x:v>
-      </x:c>
-      <x:c r="D27" s="51" t="str">
-        <x:v>階層／分組</x:v>
-      </x:c>
-      <x:c r="E27" s="56" t="str">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" ht="34" customHeight="1">
-      <x:c r="A28" s="52" t="str">
-        <x:v>Name</x:v>
-      </x:c>
-      <x:c r="B28" s="52" t="str">
-        <x:v>RD 原始／CE 保留</x:v>
-      </x:c>
-      <x:c r="C28" s="53" t="str">
-        <x:v>保留客戶 BOM 料名；每個料件列必填，不要以廠商名稱取代。</x:v>
-      </x:c>
-      <x:c r="D28" s="53" t="str">
-        <x:v>料件名稱</x:v>
-      </x:c>
-      <x:c r="E28" s="57" t="str">
-        <x:v>CAP CER 0.1UF 16V X7R</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" ht="34" customHeight="1">
-      <x:c r="A29" s="52" t="str">
-        <x:v>Qty</x:v>
-      </x:c>
-      <x:c r="B29" s="52" t="str">
-        <x:v>RD 原始／CE 保留</x:v>
-      </x:c>
-      <x:c r="C29" s="53" t="str">
-        <x:v>保留設計用量；不要因展開替代料而重算或加總用量。</x:v>
-      </x:c>
-      <x:c r="D29" s="53" t="str">
-        <x:v>數量</x:v>
-      </x:c>
-      <x:c r="E29" s="57" t="str">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" ht="34" customHeight="1">
-      <x:c r="A30" s="52" t="str">
-        <x:v>Ref Des</x:v>
-      </x:c>
-      <x:c r="B30" s="52" t="str">
-        <x:v>RD 原始／CE 保留</x:v>
-      </x:c>
-      <x:c r="C30" s="53" t="str">
-        <x:v>保留完整位號，逗號分隔；同組替代料使用相同位號。</x:v>
-      </x:c>
-      <x:c r="D30" s="53" t="str">
-        <x:v>REF DES</x:v>
-      </x:c>
-      <x:c r="E30" s="57" t="str">
-        <x:v>C101, C102</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" ht="34" customHeight="1">
-      <x:c r="A31" s="52" t="str">
-        <x:v>Manufacturer Part Number(1)</x:v>
-      </x:c>
-      <x:c r="B31" s="52" t="str">
-        <x:v>RD 提供／CE 核對</x:v>
-      </x:c>
-      <x:c r="C31" s="53" t="str">
-        <x:v>每列一個廠商料號；依原 BOM 與公司資料核對，不自行換成未確認替代料。</x:v>
-      </x:c>
-      <x:c r="D31" s="53" t="str">
-        <x:v>MPN</x:v>
-      </x:c>
-      <x:c r="E31" s="57" t="str">
-        <x:v>DEMO-CAP-001</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" ht="34" customHeight="1">
-      <x:c r="A32" s="52" t="str">
-        <x:v>Manufacturer Part Number(2)</x:v>
-      </x:c>
-      <x:c r="B32" s="52" t="str">
-        <x:v>CE 保留舊格式</x:v>
-      </x:c>
-      <x:c r="C32" s="53" t="str">
-        <x:v>舊格式相容欄，可留白；新交付的其他候選料請各自另列。</x:v>
-      </x:c>
-      <x:c r="D32" s="53" t="str">
-        <x:v>第二 MPN（相容欄）</x:v>
-      </x:c>
-      <x:c r="E32" s="57" t="str">
-        <x:v>留白</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" ht="34" customHeight="1">
-      <x:c r="A33" s="52" t="str">
-        <x:v>Manufacturer</x:v>
-      </x:c>
-      <x:c r="B33" s="52" t="str">
-        <x:v>CE 核對／帶出</x:v>
-      </x:c>
-      <x:c r="C33" s="53" t="str">
-        <x:v>填該列 MPN 對應的廠商，不把不同廠商合在同一列。</x:v>
-      </x:c>
-      <x:c r="D33" s="53" t="str">
-        <x:v>廠商</x:v>
-      </x:c>
-      <x:c r="E33" s="57" t="str">
-        <x:v>示範廠商 A</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" ht="34" customHeight="1">
-      <x:c r="A34" s="52" t="str">
-        <x:v>Sourcing Status</x:v>
-      </x:c>
-      <x:c r="B34" s="52" t="str">
-        <x:v>CE 從來源帶出</x:v>
-      </x:c>
-      <x:c r="C34" s="53" t="str">
-        <x:v>保留公司／原廠供應與核准狀態原文，例如 Approved、Active、NRND、Obsolete；不得用它取代右側零件狀態。</x:v>
-      </x:c>
-      <x:c r="D34" s="53" t="str">
-        <x:v>供應／核准狀態</x:v>
-      </x:c>
-      <x:c r="E34" s="57" t="str">
-        <x:v>Approved</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" ht="34" customHeight="1">
-      <x:c r="A35" s="52" t="str">
-        <x:v>Virtual PN</x:v>
-      </x:c>
-      <x:c r="B35" s="52" t="str">
-        <x:v>CE 從來源帶出</x:v>
-      </x:c>
-      <x:c r="C35" s="53" t="str">
-        <x:v>來源有值才帶出；無值留白，不要自編 TX。</x:v>
-      </x:c>
-      <x:c r="D35" s="53" t="str">
-        <x:v>TX（第一優先）</x:v>
-      </x:c>
-      <x:c r="E35" s="57" t="str">
-        <x:v>DEMO-TX-001</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" ht="34" customHeight="1">
-      <x:c r="A36" s="52" t="str">
-        <x:v>PEGA P/N</x:v>
-      </x:c>
-      <x:c r="B36" s="52" t="str">
-        <x:v>CE 從來源帶出</x:v>
-      </x:c>
-      <x:c r="C36" s="53" t="str">
-        <x:v>來源有值才帶出；Virtual PN 空白時才作為 TX 後備值，無值留白。</x:v>
-      </x:c>
-      <x:c r="D36" s="53" t="str">
-        <x:v>TX（第二優先）</x:v>
-      </x:c>
-      <x:c r="E36" s="57" t="str">
-        <x:v>DEMO-PEGA-001</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" ht="34" customHeight="1">
-      <x:c r="A37" s="52" t="str">
-        <x:v>Ref_tmp</x:v>
-      </x:c>
-      <x:c r="B37" s="52" t="str">
-        <x:v>原始分組／CE 保留</x:v>
-      </x:c>
-      <x:c r="C37" s="53" t="str">
-        <x:v>可留白由工具依 Ref Des 分組；本範本若填寫，使用與 Ref Des 相同的完整位號集合，同組替代料相鄰排列。</x:v>
-      </x:c>
-      <x:c r="D37" s="53" t="str">
-        <x:v>Ref Group</x:v>
-      </x:c>
-      <x:c r="E37" s="57" t="str">
-        <x:v>C101, C102</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" ht="34" customHeight="1">
-      <x:c r="A38" s="52" t="str">
-        <x:v>LV</x:v>
-      </x:c>
-      <x:c r="B38" s="52" t="str">
-        <x:v>來源資料／CE 保留</x:v>
-      </x:c>
-      <x:c r="C38" s="53" t="str">
-        <x:v>來源有版次就保留，不另造版本。</x:v>
-      </x:c>
-      <x:c r="D38" s="53" t="str">
-        <x:v>版次</x:v>
-      </x:c>
-      <x:c r="E38" s="57" t="str">
-        <x:v>A</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" ht="34" customHeight="1">
-      <x:c r="A39" s="52" t="str">
-        <x:v>CIS/Remark</x:v>
-      </x:c>
-      <x:c r="B39" s="52" t="str">
-        <x:v>來源參考／CE 保留</x:v>
-      </x:c>
-      <x:c r="C39" s="53" t="str">
-        <x:v>只供原 Excel 參考；網站不匯入此欄，也不把它當成 RD 追蹤說明。</x:v>
-      </x:c>
-      <x:c r="D39" s="53" t="str">
-        <x:v>不匯入</x:v>
-      </x:c>
-      <x:c r="E39" s="57" t="str">
-        <x:v>來源備註（選填）</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" ht="34" customHeight="1">
-      <x:c r="A40" s="52" t="str">
-        <x:v>Part Number</x:v>
-      </x:c>
-      <x:c r="B40" s="52" t="str">
-        <x:v>CE 從公司系統帶出</x:v>
-      </x:c>
-      <x:c r="C40" s="53" t="str">
-        <x:v>填公司正式料號並保留前導零；查無時留白，於零件狀態填待確認，不把廠商 MPN／TX 填進這欄。</x:v>
-      </x:c>
-      <x:c r="D40" s="53" t="str">
-        <x:v>內部料號</x:v>
-      </x:c>
-      <x:c r="E40" s="57" t="str">
-        <x:v>000-DEMO-001</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" ht="34" customHeight="1">
-      <x:c r="A41" s="52" t="str">
-        <x:v>Part Name</x:v>
-      </x:c>
-      <x:c r="B41" s="52" t="str">
-        <x:v>CE 從公司系統帶出</x:v>
-      </x:c>
-      <x:c r="C41" s="53" t="str">
-        <x:v>來源有公司料名就保留；無資料可留白。</x:v>
-      </x:c>
-      <x:c r="D41" s="53" t="str">
-        <x:v>內部料名</x:v>
-      </x:c>
-      <x:c r="E41" s="57" t="str">
-        <x:v>示範電容</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" ht="34" customHeight="1">
-      <x:c r="A42" s="52" t="str">
-        <x:v>Part Spec</x:v>
-      </x:c>
-      <x:c r="B42" s="52" t="str">
-        <x:v>RD 原始／CE 保留</x:v>
-      </x:c>
-      <x:c r="C42" s="53" t="str">
-        <x:v>保留原規格；同組資料維持一致，差異交 RD 確認。</x:v>
-      </x:c>
-      <x:c r="D42" s="53" t="str">
-        <x:v>規格</x:v>
-      </x:c>
-      <x:c r="E42" s="57" t="str">
-        <x:v>0.1uF / 16V / X7R</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" ht="34" customHeight="1">
-      <x:c r="A43" s="52" t="str">
-        <x:v>Schematic_Part</x:v>
-      </x:c>
-      <x:c r="B43" s="52" t="str">
-        <x:v>RD 原始／CE 保留</x:v>
-      </x:c>
-      <x:c r="C43" s="53" t="str">
-        <x:v>原 BOM 有原理圖符號就保留；無資料可留白，不要求 CE 新建符號。</x:v>
-      </x:c>
-      <x:c r="D43" s="53" t="str">
-        <x:v>Symbol</x:v>
-      </x:c>
-      <x:c r="E43" s="57" t="str">
-        <x:v>CAP</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" ht="34" customHeight="1">
-      <x:c r="A44" s="52" t="str">
-        <x:v>PCB_Footprint</x:v>
-      </x:c>
-      <x:c r="B44" s="52" t="str">
-        <x:v>RD 原始／CE 保留</x:v>
-      </x:c>
-      <x:c r="C44" s="53" t="str">
-        <x:v>原 BOM 有封裝就保留；無資料可留白，不要求 CE 新建封裝。</x:v>
-      </x:c>
-      <x:c r="D44" s="53" t="str">
-        <x:v>Footprint</x:v>
-      </x:c>
-      <x:c r="E44" s="57" t="str">
-        <x:v>C_0402</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" ht="34" customHeight="1">
-      <x:c r="A45" s="54" t="str">
-        <x:v>零件狀態</x:v>
-      </x:c>
-      <x:c r="B45" s="54" t="str">
-        <x:v>CE 補欄／帶出原文</x:v>
-      </x:c>
-      <x:c r="C45" s="55" t="str">
-        <x:v>本次交付必須補在最右側。填公司新設計使用限制原文；不明填待確認，供 RD 後續確認與參考。</x:v>
-      </x:c>
-      <x:c r="D45" s="55" t="str">
-        <x:v>零件狀態（獨立顯示）</x:v>
-      </x:c>
-      <x:c r="E45" s="58" t="str">
-        <x:v>新設計產品不建議使用－ODM 不建議用料</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
 </file>
--- a/public/material-upload-template.xlsx
+++ b/public/material-upload-template.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上傳資料" sheetId="1" r:id="R3e7c563ac3fa4ea7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上傳資料" sheetId="1" r:id="R2d091ca528e54fb3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -502,11 +502,12 @@
     <x:col min="12" max="12" width="12" hidden="0" customWidth="1"/>
     <x:col min="13" max="13" width="30" hidden="0" customWidth="1"/>
     <x:col min="14" max="14" width="25" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="25" hidden="0" customWidth="1"/>
-    <x:col min="16" max="16" width="30" hidden="0" customWidth="1"/>
-    <x:col min="17" max="17" width="25" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="26" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="25" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="30" hidden="0" customWidth="1"/>
     <x:col min="18" max="18" width="25" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="45" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="25" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="45" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
@@ -531,6 +532,7 @@
       <x:c r="Q1" s="6"/>
       <x:c r="R1" s="6"/>
       <x:c r="S1" s="6"/>
+      <x:c r="T1" s="6"/>
     </x:row>
     <x:row r="2" ht="27" customHeight="1">
       <x:c r="A2" s="7" t="str">
@@ -554,6 +556,7 @@
       <x:c r="Q2" s="3"/>
       <x:c r="R2" s="3"/>
       <x:c r="S2" s="3"/>
+      <x:c r="T2" s="3"/>
     </x:row>
     <x:row r="3" ht="10" customHeight="1">
       <x:c r="A3" s="1"/>
@@ -575,6 +578,7 @@
       <x:c r="Q3" s="1"/>
       <x:c r="R3" s="1"/>
       <x:c r="S3" s="1"/>
+      <x:c r="T3" s="1"/>
     </x:row>
     <x:row r="4" ht="42" customHeight="1">
       <x:c r="A4" s="21" t="str">
@@ -620,18 +624,21 @@
         <x:v>Part Number</x:v>
       </x:c>
       <x:c r="O4" s="22" t="str">
+        <x:v>Symbol</x:v>
+      </x:c>
+      <x:c r="P4" s="22" t="str">
         <x:v>Part Name</x:v>
       </x:c>
-      <x:c r="P4" s="22" t="str">
+      <x:c r="Q4" s="22" t="str">
         <x:v>Part Spec</x:v>
       </x:c>
-      <x:c r="Q4" s="22" t="str">
+      <x:c r="R4" s="22" t="str">
         <x:v>Schematic_Part</x:v>
       </x:c>
-      <x:c r="R4" s="22" t="str">
+      <x:c r="S4" s="22" t="str">
         <x:v>PCB_Footprint</x:v>
       </x:c>
-      <x:c r="S4" s="23" t="str">
+      <x:c r="T4" s="23" t="str">
         <x:v>零件狀態</x:v>
       </x:c>
     </x:row>
@@ -655,6 +662,7 @@
       <x:c r="Q5" s="30"/>
       <x:c r="R5" s="30"/>
       <x:c r="S5" s="30"/>
+      <x:c r="T5" s="30"/>
     </x:row>
     <x:row r="6" ht="24" customHeight="1">
       <x:c r="A6" s="40"/>
@@ -676,6 +684,7 @@
       <x:c r="Q6" s="31"/>
       <x:c r="R6" s="31"/>
       <x:c r="S6" s="31"/>
+      <x:c r="T6" s="31"/>
     </x:row>
     <x:row r="7" ht="24" customHeight="1">
       <x:c r="A7" s="40"/>
@@ -697,6 +706,7 @@
       <x:c r="Q7" s="31"/>
       <x:c r="R7" s="31"/>
       <x:c r="S7" s="31"/>
+      <x:c r="T7" s="31"/>
     </x:row>
     <x:row r="8" ht="24" customHeight="1">
       <x:c r="A8" s="40"/>
@@ -718,6 +728,7 @@
       <x:c r="Q8" s="31"/>
       <x:c r="R8" s="31"/>
       <x:c r="S8" s="31"/>
+      <x:c r="T8" s="31"/>
     </x:row>
     <x:row r="9" ht="24" customHeight="1">
       <x:c r="A9" s="40"/>
@@ -739,6 +750,7 @@
       <x:c r="Q9" s="31"/>
       <x:c r="R9" s="31"/>
       <x:c r="S9" s="31"/>
+      <x:c r="T9" s="31"/>
     </x:row>
     <x:row r="10" ht="24" customHeight="1">
       <x:c r="A10" s="40"/>
@@ -760,6 +772,7 @@
       <x:c r="Q10" s="31"/>
       <x:c r="R10" s="31"/>
       <x:c r="S10" s="31"/>
+      <x:c r="T10" s="31"/>
     </x:row>
     <x:row r="11" ht="24" customHeight="1">
       <x:c r="A11" s="40"/>
@@ -781,6 +794,7 @@
       <x:c r="Q11" s="31"/>
       <x:c r="R11" s="31"/>
       <x:c r="S11" s="31"/>
+      <x:c r="T11" s="31"/>
     </x:row>
     <x:row r="12" ht="24" customHeight="1">
       <x:c r="A12" s="40"/>
@@ -802,6 +816,7 @@
       <x:c r="Q12" s="31"/>
       <x:c r="R12" s="31"/>
       <x:c r="S12" s="31"/>
+      <x:c r="T12" s="31"/>
     </x:row>
     <x:row r="13" ht="24" customHeight="1">
       <x:c r="A13" s="40"/>
@@ -823,6 +838,7 @@
       <x:c r="Q13" s="31"/>
       <x:c r="R13" s="31"/>
       <x:c r="S13" s="31"/>
+      <x:c r="T13" s="31"/>
     </x:row>
     <x:row r="14" ht="24" customHeight="1">
       <x:c r="A14" s="40"/>
@@ -844,6 +860,7 @@
       <x:c r="Q14" s="31"/>
       <x:c r="R14" s="31"/>
       <x:c r="S14" s="31"/>
+      <x:c r="T14" s="31"/>
     </x:row>
     <x:row r="15" ht="24" customHeight="1">
       <x:c r="A15" s="40"/>
@@ -865,6 +882,7 @@
       <x:c r="Q15" s="31"/>
       <x:c r="R15" s="31"/>
       <x:c r="S15" s="31"/>
+      <x:c r="T15" s="31"/>
     </x:row>
     <x:row r="16" ht="24" customHeight="1">
       <x:c r="A16" s="40"/>
@@ -886,6 +904,7 @@
       <x:c r="Q16" s="31"/>
       <x:c r="R16" s="31"/>
       <x:c r="S16" s="31"/>
+      <x:c r="T16" s="31"/>
     </x:row>
     <x:row r="17" ht="24" customHeight="1">
       <x:c r="A17" s="40"/>
@@ -907,6 +926,7 @@
       <x:c r="Q17" s="31"/>
       <x:c r="R17" s="31"/>
       <x:c r="S17" s="31"/>
+      <x:c r="T17" s="31"/>
     </x:row>
     <x:row r="18" ht="24" customHeight="1">
       <x:c r="A18" s="40"/>
@@ -928,6 +948,7 @@
       <x:c r="Q18" s="31"/>
       <x:c r="R18" s="31"/>
       <x:c r="S18" s="31"/>
+      <x:c r="T18" s="31"/>
     </x:row>
     <x:row r="19" ht="24" customHeight="1">
       <x:c r="A19" s="40"/>
@@ -949,6 +970,7 @@
       <x:c r="Q19" s="31"/>
       <x:c r="R19" s="31"/>
       <x:c r="S19" s="31"/>
+      <x:c r="T19" s="31"/>
     </x:row>
     <x:row r="20" ht="24" customHeight="1">
       <x:c r="A20" s="40"/>
@@ -970,6 +992,7 @@
       <x:c r="Q20" s="31"/>
       <x:c r="R20" s="31"/>
       <x:c r="S20" s="31"/>
+      <x:c r="T20" s="31"/>
     </x:row>
     <x:row r="21" ht="24" customHeight="1">
       <x:c r="A21" s="40"/>
@@ -991,6 +1014,7 @@
       <x:c r="Q21" s="31"/>
       <x:c r="R21" s="31"/>
       <x:c r="S21" s="31"/>
+      <x:c r="T21" s="31"/>
     </x:row>
     <x:row r="22" ht="24" customHeight="1">
       <x:c r="A22" s="40"/>
@@ -1012,6 +1036,7 @@
       <x:c r="Q22" s="31"/>
       <x:c r="R22" s="31"/>
       <x:c r="S22" s="31"/>
+      <x:c r="T22" s="31"/>
     </x:row>
     <x:row r="23" ht="24" customHeight="1">
       <x:c r="A23" s="40"/>
@@ -1033,6 +1058,7 @@
       <x:c r="Q23" s="31"/>
       <x:c r="R23" s="31"/>
       <x:c r="S23" s="31"/>
+      <x:c r="T23" s="31"/>
     </x:row>
     <x:row r="24" ht="24" customHeight="1">
       <x:c r="A24" s="40"/>
@@ -1054,6 +1080,7 @@
       <x:c r="Q24" s="31"/>
       <x:c r="R24" s="31"/>
       <x:c r="S24" s="31"/>
+      <x:c r="T24" s="31"/>
     </x:row>
     <x:row r="25" ht="24" customHeight="1">
       <x:c r="A25" s="40"/>
@@ -1075,6 +1102,7 @@
       <x:c r="Q25" s="31"/>
       <x:c r="R25" s="31"/>
       <x:c r="S25" s="31"/>
+      <x:c r="T25" s="31"/>
     </x:row>
     <x:row r="26" ht="24" customHeight="1">
       <x:c r="A26" s="40"/>
@@ -1096,6 +1124,7 @@
       <x:c r="Q26" s="31"/>
       <x:c r="R26" s="31"/>
       <x:c r="S26" s="31"/>
+      <x:c r="T26" s="31"/>
     </x:row>
     <x:row r="27" ht="24" customHeight="1">
       <x:c r="A27" s="40"/>
@@ -1117,6 +1146,7 @@
       <x:c r="Q27" s="31"/>
       <x:c r="R27" s="31"/>
       <x:c r="S27" s="31"/>
+      <x:c r="T27" s="31"/>
     </x:row>
     <x:row r="28" ht="24" customHeight="1">
       <x:c r="A28" s="40"/>
@@ -1138,6 +1168,7 @@
       <x:c r="Q28" s="31"/>
       <x:c r="R28" s="31"/>
       <x:c r="S28" s="31"/>
+      <x:c r="T28" s="31"/>
     </x:row>
     <x:row r="29" ht="24" customHeight="1">
       <x:c r="A29" s="40"/>
@@ -1159,6 +1190,7 @@
       <x:c r="Q29" s="31"/>
       <x:c r="R29" s="31"/>
       <x:c r="S29" s="31"/>
+      <x:c r="T29" s="31"/>
     </x:row>
     <x:row r="30" ht="24" customHeight="1">
       <x:c r="A30" s="40"/>
@@ -1180,6 +1212,7 @@
       <x:c r="Q30" s="31"/>
       <x:c r="R30" s="31"/>
       <x:c r="S30" s="31"/>
+      <x:c r="T30" s="31"/>
     </x:row>
     <x:row r="31" ht="24" customHeight="1">
       <x:c r="A31" s="40"/>
@@ -1201,6 +1234,7 @@
       <x:c r="Q31" s="31"/>
       <x:c r="R31" s="31"/>
       <x:c r="S31" s="31"/>
+      <x:c r="T31" s="31"/>
     </x:row>
     <x:row r="32" ht="24" customHeight="1">
       <x:c r="A32" s="40"/>
@@ -1222,6 +1256,7 @@
       <x:c r="Q32" s="31"/>
       <x:c r="R32" s="31"/>
       <x:c r="S32" s="31"/>
+      <x:c r="T32" s="31"/>
     </x:row>
     <x:row r="33" ht="24" customHeight="1">
       <x:c r="A33" s="40"/>
@@ -1243,6 +1278,7 @@
       <x:c r="Q33" s="31"/>
       <x:c r="R33" s="31"/>
       <x:c r="S33" s="31"/>
+      <x:c r="T33" s="31"/>
     </x:row>
     <x:row r="34" ht="24" customHeight="1">
       <x:c r="A34" s="41"/>
@@ -1264,6 +1300,7 @@
       <x:c r="Q34" s="32"/>
       <x:c r="R34" s="32"/>
       <x:c r="S34" s="32"/>
+      <x:c r="T34" s="32"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/material-upload-template.xlsx
+++ b/public/material-upload-template.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上傳資料" sheetId="1" r:id="R2d091ca528e54fb3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上傳資料" sheetId="1" r:id="Rf21fcfc5a3ff41e2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -493,21 +493,16 @@
     <x:col min="3" max="3" width="12" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="32" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="32" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="24" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="24" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="25" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="25" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="23" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="23" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="28" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="26" hidden="0" customWidth="1"/>
     <x:col min="11" max="11" width="25" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="12" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="30" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="30" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="25" hidden="0" customWidth="1"/>
     <x:col min="14" max="14" width="25" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="26" hidden="0" customWidth="1"/>
-    <x:col min="16" max="16" width="25" hidden="0" customWidth="1"/>
-    <x:col min="17" max="17" width="30" hidden="0" customWidth="1"/>
-    <x:col min="18" max="18" width="25" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="25" hidden="0" customWidth="1"/>
-    <x:col min="20" max="20" width="45" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="45" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
@@ -528,11 +523,6 @@
       <x:c r="M1" s="6"/>
       <x:c r="N1" s="6"/>
       <x:c r="O1" s="6"/>
-      <x:c r="P1" s="6"/>
-      <x:c r="Q1" s="6"/>
-      <x:c r="R1" s="6"/>
-      <x:c r="S1" s="6"/>
-      <x:c r="T1" s="6"/>
     </x:row>
     <x:row r="2" ht="27" customHeight="1">
       <x:c r="A2" s="7" t="str">
@@ -552,11 +542,6 @@
       <x:c r="M2" s="3"/>
       <x:c r="N2" s="3"/>
       <x:c r="O2" s="3"/>
-      <x:c r="P2" s="3"/>
-      <x:c r="Q2" s="3"/>
-      <x:c r="R2" s="3"/>
-      <x:c r="S2" s="3"/>
-      <x:c r="T2" s="3"/>
     </x:row>
     <x:row r="3" ht="10" customHeight="1">
       <x:c r="A3" s="1"/>
@@ -574,11 +559,6 @@
       <x:c r="M3" s="1"/>
       <x:c r="N3" s="1"/>
       <x:c r="O3" s="1"/>
-      <x:c r="P3" s="1"/>
-      <x:c r="Q3" s="1"/>
-      <x:c r="R3" s="1"/>
-      <x:c r="S3" s="1"/>
-      <x:c r="T3" s="1"/>
     </x:row>
     <x:row r="4" ht="42" customHeight="1">
       <x:c r="A4" s="21" t="str">
@@ -594,51 +574,36 @@
         <x:v>Ref Des</x:v>
       </x:c>
       <x:c r="E4" s="22" t="str">
-        <x:v>Manufacturer Part Number(1)</x:v>
+        <x:v>Manufacturer Part Number</x:v>
       </x:c>
       <x:c r="F4" s="22" t="str">
-        <x:v>Manufacturer Part Number(2)</x:v>
+        <x:v>Manufacturer</x:v>
       </x:c>
       <x:c r="G4" s="22" t="str">
-        <x:v>Manufacturer</x:v>
+        <x:v>Sourcing Status</x:v>
       </x:c>
       <x:c r="H4" s="22" t="str">
-        <x:v>Sourcing Status</x:v>
+        <x:v>虛擬料號</x:v>
       </x:c>
       <x:c r="I4" s="22" t="str">
-        <x:v>Virtual PN</x:v>
+        <x:v>實體料號</x:v>
       </x:c>
       <x:c r="J4" s="22" t="str">
-        <x:v>PEGA P/N</x:v>
+        <x:v>Symbol</x:v>
       </x:c>
       <x:c r="K4" s="22" t="str">
-        <x:v>Ref_tmp</x:v>
+        <x:v>Part Name</x:v>
       </x:c>
       <x:c r="L4" s="22" t="str">
-        <x:v>LV</x:v>
+        <x:v>Part Spec</x:v>
       </x:c>
       <x:c r="M4" s="22" t="str">
-        <x:v>CIS/Remark</x:v>
+        <x:v>Schematic_Part</x:v>
       </x:c>
       <x:c r="N4" s="22" t="str">
-        <x:v>Part Number</x:v>
-      </x:c>
-      <x:c r="O4" s="22" t="str">
-        <x:v>Symbol</x:v>
-      </x:c>
-      <x:c r="P4" s="22" t="str">
-        <x:v>Part Name</x:v>
-      </x:c>
-      <x:c r="Q4" s="22" t="str">
-        <x:v>Part Spec</x:v>
-      </x:c>
-      <x:c r="R4" s="22" t="str">
-        <x:v>Schematic_Part</x:v>
-      </x:c>
-      <x:c r="S4" s="22" t="str">
         <x:v>PCB_Footprint</x:v>
       </x:c>
-      <x:c r="T4" s="23" t="str">
+      <x:c r="O4" s="23" t="str">
         <x:v>零件狀態</x:v>
       </x:c>
     </x:row>
@@ -658,11 +623,6 @@
       <x:c r="M5" s="30"/>
       <x:c r="N5" s="30"/>
       <x:c r="O5" s="30"/>
-      <x:c r="P5" s="30"/>
-      <x:c r="Q5" s="30"/>
-      <x:c r="R5" s="30"/>
-      <x:c r="S5" s="30"/>
-      <x:c r="T5" s="30"/>
     </x:row>
     <x:row r="6" ht="24" customHeight="1">
       <x:c r="A6" s="40"/>
@@ -680,11 +640,6 @@
       <x:c r="M6" s="31"/>
       <x:c r="N6" s="31"/>
       <x:c r="O6" s="31"/>
-      <x:c r="P6" s="31"/>
-      <x:c r="Q6" s="31"/>
-      <x:c r="R6" s="31"/>
-      <x:c r="S6" s="31"/>
-      <x:c r="T6" s="31"/>
     </x:row>
     <x:row r="7" ht="24" customHeight="1">
       <x:c r="A7" s="40"/>
@@ -702,11 +657,6 @@
       <x:c r="M7" s="31"/>
       <x:c r="N7" s="31"/>
       <x:c r="O7" s="31"/>
-      <x:c r="P7" s="31"/>
-      <x:c r="Q7" s="31"/>
-      <x:c r="R7" s="31"/>
-      <x:c r="S7" s="31"/>
-      <x:c r="T7" s="31"/>
     </x:row>
     <x:row r="8" ht="24" customHeight="1">
       <x:c r="A8" s="40"/>
@@ -724,11 +674,6 @@
       <x:c r="M8" s="31"/>
       <x:c r="N8" s="31"/>
       <x:c r="O8" s="31"/>
-      <x:c r="P8" s="31"/>
-      <x:c r="Q8" s="31"/>
-      <x:c r="R8" s="31"/>
-      <x:c r="S8" s="31"/>
-      <x:c r="T8" s="31"/>
     </x:row>
     <x:row r="9" ht="24" customHeight="1">
       <x:c r="A9" s="40"/>
@@ -746,11 +691,6 @@
       <x:c r="M9" s="31"/>
       <x:c r="N9" s="31"/>
       <x:c r="O9" s="31"/>
-      <x:c r="P9" s="31"/>
-      <x:c r="Q9" s="31"/>
-      <x:c r="R9" s="31"/>
-      <x:c r="S9" s="31"/>
-      <x:c r="T9" s="31"/>
     </x:row>
     <x:row r="10" ht="24" customHeight="1">
       <x:c r="A10" s="40"/>
@@ -768,11 +708,6 @@
       <x:c r="M10" s="31"/>
       <x:c r="N10" s="31"/>
       <x:c r="O10" s="31"/>
-      <x:c r="P10" s="31"/>
-      <x:c r="Q10" s="31"/>
-      <x:c r="R10" s="31"/>
-      <x:c r="S10" s="31"/>
-      <x:c r="T10" s="31"/>
     </x:row>
     <x:row r="11" ht="24" customHeight="1">
       <x:c r="A11" s="40"/>
@@ -790,11 +725,6 @@
       <x:c r="M11" s="31"/>
       <x:c r="N11" s="31"/>
       <x:c r="O11" s="31"/>
-      <x:c r="P11" s="31"/>
-      <x:c r="Q11" s="31"/>
-      <x:c r="R11" s="31"/>
-      <x:c r="S11" s="31"/>
-      <x:c r="T11" s="31"/>
     </x:row>
     <x:row r="12" ht="24" customHeight="1">
       <x:c r="A12" s="40"/>
@@ -812,11 +742,6 @@
       <x:c r="M12" s="31"/>
       <x:c r="N12" s="31"/>
       <x:c r="O12" s="31"/>
-      <x:c r="P12" s="31"/>
-      <x:c r="Q12" s="31"/>
-      <x:c r="R12" s="31"/>
-      <x:c r="S12" s="31"/>
-      <x:c r="T12" s="31"/>
     </x:row>
     <x:row r="13" ht="24" customHeight="1">
       <x:c r="A13" s="40"/>
@@ -834,11 +759,6 @@
       <x:c r="M13" s="31"/>
       <x:c r="N13" s="31"/>
       <x:c r="O13" s="31"/>
-      <x:c r="P13" s="31"/>
-      <x:c r="Q13" s="31"/>
-      <x:c r="R13" s="31"/>
-      <x:c r="S13" s="31"/>
-      <x:c r="T13" s="31"/>
     </x:row>
     <x:row r="14" ht="24" customHeight="1">
       <x:c r="A14" s="40"/>
@@ -856,11 +776,6 @@
       <x:c r="M14" s="31"/>
       <x:c r="N14" s="31"/>
       <x:c r="O14" s="31"/>
-      <x:c r="P14" s="31"/>
-      <x:c r="Q14" s="31"/>
-      <x:c r="R14" s="31"/>
-      <x:c r="S14" s="31"/>
-      <x:c r="T14" s="31"/>
     </x:row>
     <x:row r="15" ht="24" customHeight="1">
       <x:c r="A15" s="40"/>
@@ -878,11 +793,6 @@
       <x:c r="M15" s="31"/>
       <x:c r="N15" s="31"/>
       <x:c r="O15" s="31"/>
-      <x:c r="P15" s="31"/>
-      <x:c r="Q15" s="31"/>
-      <x:c r="R15" s="31"/>
-      <x:c r="S15" s="31"/>
-      <x:c r="T15" s="31"/>
     </x:row>
     <x:row r="16" ht="24" customHeight="1">
       <x:c r="A16" s="40"/>
@@ -900,11 +810,6 @@
       <x:c r="M16" s="31"/>
       <x:c r="N16" s="31"/>
       <x:c r="O16" s="31"/>
-      <x:c r="P16" s="31"/>
-      <x:c r="Q16" s="31"/>
-      <x:c r="R16" s="31"/>
-      <x:c r="S16" s="31"/>
-      <x:c r="T16" s="31"/>
     </x:row>
     <x:row r="17" ht="24" customHeight="1">
       <x:c r="A17" s="40"/>
@@ -922,11 +827,6 @@
       <x:c r="M17" s="31"/>
       <x:c r="N17" s="31"/>
       <x:c r="O17" s="31"/>
-      <x:c r="P17" s="31"/>
-      <x:c r="Q17" s="31"/>
-      <x:c r="R17" s="31"/>
-      <x:c r="S17" s="31"/>
-      <x:c r="T17" s="31"/>
     </x:row>
     <x:row r="18" ht="24" customHeight="1">
       <x:c r="A18" s="40"/>
@@ -944,11 +844,6 @@
       <x:c r="M18" s="31"/>
       <x:c r="N18" s="31"/>
       <x:c r="O18" s="31"/>
-      <x:c r="P18" s="31"/>
-      <x:c r="Q18" s="31"/>
-      <x:c r="R18" s="31"/>
-      <x:c r="S18" s="31"/>
-      <x:c r="T18" s="31"/>
     </x:row>
     <x:row r="19" ht="24" customHeight="1">
       <x:c r="A19" s="40"/>
@@ -966,11 +861,6 @@
       <x:c r="M19" s="31"/>
       <x:c r="N19" s="31"/>
       <x:c r="O19" s="31"/>
-      <x:c r="P19" s="31"/>
-      <x:c r="Q19" s="31"/>
-      <x:c r="R19" s="31"/>
-      <x:c r="S19" s="31"/>
-      <x:c r="T19" s="31"/>
     </x:row>
     <x:row r="20" ht="24" customHeight="1">
       <x:c r="A20" s="40"/>
@@ -988,11 +878,6 @@
       <x:c r="M20" s="31"/>
       <x:c r="N20" s="31"/>
       <x:c r="O20" s="31"/>
-      <x:c r="P20" s="31"/>
-      <x:c r="Q20" s="31"/>
-      <x:c r="R20" s="31"/>
-      <x:c r="S20" s="31"/>
-      <x:c r="T20" s="31"/>
     </x:row>
     <x:row r="21" ht="24" customHeight="1">
       <x:c r="A21" s="40"/>
@@ -1010,11 +895,6 @@
       <x:c r="M21" s="31"/>
       <x:c r="N21" s="31"/>
       <x:c r="O21" s="31"/>
-      <x:c r="P21" s="31"/>
-      <x:c r="Q21" s="31"/>
-      <x:c r="R21" s="31"/>
-      <x:c r="S21" s="31"/>
-      <x:c r="T21" s="31"/>
     </x:row>
     <x:row r="22" ht="24" customHeight="1">
       <x:c r="A22" s="40"/>
@@ -1032,11 +912,6 @@
       <x:c r="M22" s="31"/>
       <x:c r="N22" s="31"/>
       <x:c r="O22" s="31"/>
-      <x:c r="P22" s="31"/>
-      <x:c r="Q22" s="31"/>
-      <x:c r="R22" s="31"/>
-      <x:c r="S22" s="31"/>
-      <x:c r="T22" s="31"/>
     </x:row>
     <x:row r="23" ht="24" customHeight="1">
       <x:c r="A23" s="40"/>
@@ -1054,11 +929,6 @@
       <x:c r="M23" s="31"/>
       <x:c r="N23" s="31"/>
       <x:c r="O23" s="31"/>
-      <x:c r="P23" s="31"/>
-      <x:c r="Q23" s="31"/>
-      <x:c r="R23" s="31"/>
-      <x:c r="S23" s="31"/>
-      <x:c r="T23" s="31"/>
     </x:row>
     <x:row r="24" ht="24" customHeight="1">
       <x:c r="A24" s="40"/>
@@ -1076,11 +946,6 @@
       <x:c r="M24" s="31"/>
       <x:c r="N24" s="31"/>
       <x:c r="O24" s="31"/>
-      <x:c r="P24" s="31"/>
-      <x:c r="Q24" s="31"/>
-      <x:c r="R24" s="31"/>
-      <x:c r="S24" s="31"/>
-      <x:c r="T24" s="31"/>
     </x:row>
     <x:row r="25" ht="24" customHeight="1">
       <x:c r="A25" s="40"/>
@@ -1098,11 +963,6 @@
       <x:c r="M25" s="31"/>
       <x:c r="N25" s="31"/>
       <x:c r="O25" s="31"/>
-      <x:c r="P25" s="31"/>
-      <x:c r="Q25" s="31"/>
-      <x:c r="R25" s="31"/>
-      <x:c r="S25" s="31"/>
-      <x:c r="T25" s="31"/>
     </x:row>
     <x:row r="26" ht="24" customHeight="1">
       <x:c r="A26" s="40"/>
@@ -1120,11 +980,6 @@
       <x:c r="M26" s="31"/>
       <x:c r="N26" s="31"/>
       <x:c r="O26" s="31"/>
-      <x:c r="P26" s="31"/>
-      <x:c r="Q26" s="31"/>
-      <x:c r="R26" s="31"/>
-      <x:c r="S26" s="31"/>
-      <x:c r="T26" s="31"/>
     </x:row>
     <x:row r="27" ht="24" customHeight="1">
       <x:c r="A27" s="40"/>
@@ -1142,11 +997,6 @@
       <x:c r="M27" s="31"/>
       <x:c r="N27" s="31"/>
       <x:c r="O27" s="31"/>
-      <x:c r="P27" s="31"/>
-      <x:c r="Q27" s="31"/>
-      <x:c r="R27" s="31"/>
-      <x:c r="S27" s="31"/>
-      <x:c r="T27" s="31"/>
     </x:row>
     <x:row r="28" ht="24" customHeight="1">
       <x:c r="A28" s="40"/>
@@ -1164,11 +1014,6 @@
       <x:c r="M28" s="31"/>
       <x:c r="N28" s="31"/>
       <x:c r="O28" s="31"/>
-      <x:c r="P28" s="31"/>
-      <x:c r="Q28" s="31"/>
-      <x:c r="R28" s="31"/>
-      <x:c r="S28" s="31"/>
-      <x:c r="T28" s="31"/>
     </x:row>
     <x:row r="29" ht="24" customHeight="1">
       <x:c r="A29" s="40"/>
@@ -1186,11 +1031,6 @@
       <x:c r="M29" s="31"/>
       <x:c r="N29" s="31"/>
       <x:c r="O29" s="31"/>
-      <x:c r="P29" s="31"/>
-      <x:c r="Q29" s="31"/>
-      <x:c r="R29" s="31"/>
-      <x:c r="S29" s="31"/>
-      <x:c r="T29" s="31"/>
     </x:row>
     <x:row r="30" ht="24" customHeight="1">
       <x:c r="A30" s="40"/>
@@ -1208,11 +1048,6 @@
       <x:c r="M30" s="31"/>
       <x:c r="N30" s="31"/>
       <x:c r="O30" s="31"/>
-      <x:c r="P30" s="31"/>
-      <x:c r="Q30" s="31"/>
-      <x:c r="R30" s="31"/>
-      <x:c r="S30" s="31"/>
-      <x:c r="T30" s="31"/>
     </x:row>
     <x:row r="31" ht="24" customHeight="1">
       <x:c r="A31" s="40"/>
@@ -1230,11 +1065,6 @@
       <x:c r="M31" s="31"/>
       <x:c r="N31" s="31"/>
       <x:c r="O31" s="31"/>
-      <x:c r="P31" s="31"/>
-      <x:c r="Q31" s="31"/>
-      <x:c r="R31" s="31"/>
-      <x:c r="S31" s="31"/>
-      <x:c r="T31" s="31"/>
     </x:row>
     <x:row r="32" ht="24" customHeight="1">
       <x:c r="A32" s="40"/>
@@ -1252,11 +1082,6 @@
       <x:c r="M32" s="31"/>
       <x:c r="N32" s="31"/>
       <x:c r="O32" s="31"/>
-      <x:c r="P32" s="31"/>
-      <x:c r="Q32" s="31"/>
-      <x:c r="R32" s="31"/>
-      <x:c r="S32" s="31"/>
-      <x:c r="T32" s="31"/>
     </x:row>
     <x:row r="33" ht="24" customHeight="1">
       <x:c r="A33" s="40"/>
@@ -1274,11 +1099,6 @@
       <x:c r="M33" s="31"/>
       <x:c r="N33" s="31"/>
       <x:c r="O33" s="31"/>
-      <x:c r="P33" s="31"/>
-      <x:c r="Q33" s="31"/>
-      <x:c r="R33" s="31"/>
-      <x:c r="S33" s="31"/>
-      <x:c r="T33" s="31"/>
     </x:row>
     <x:row r="34" ht="24" customHeight="1">
       <x:c r="A34" s="41"/>
@@ -1296,11 +1116,6 @@
       <x:c r="M34" s="32"/>
       <x:c r="N34" s="32"/>
       <x:c r="O34" s="32"/>
-      <x:c r="P34" s="32"/>
-      <x:c r="Q34" s="32"/>
-      <x:c r="R34" s="32"/>
-      <x:c r="S34" s="32"/>
-      <x:c r="T34" s="32"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/material-upload-template.xlsx
+++ b/public/material-upload-template.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上傳資料" sheetId="1" r:id="Rf21fcfc5a3ff41e2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上傳資料" sheetId="1" r:id="Red38577058ca4bae"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,7 +18,7 @@
     <x:numFmt numFmtId="201" formatCode="0"/>
     <x:numFmt numFmtId="202" formatCode="General"/>
   </x:numFmts>
-  <x:fonts count="5">
+  <x:fonts count="6">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -45,8 +45,13 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Arial"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF43566A"/>
+      <x:name val="Arial"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="6">
+  <x:fills count="7">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -73,8 +78,13 @@
         <x:fgColor rgb="FF30353B"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF0F6"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="8">
+  <x:borders count="11">
     <x:border>
       <x:left/>
       <x:right/>
@@ -122,6 +132,41 @@
     </x:border>
     <x:border>
       <x:left/>
+      <x:right style="thin">
+        <x:color rgb="FFFFFFFF"/>
+      </x:right>
+      <x:top/>
+      <x:bottom style="thin">
+        <x:color rgb="FFCDD7E2"/>
+      </x:bottom>
+      <x:diagonal/>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFFFFFFF"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFFFFFFF"/>
+      </x:right>
+      <x:top/>
+      <x:bottom style="thin">
+        <x:color rgb="FFCDD7E2"/>
+      </x:bottom>
+      <x:diagonal/>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFFFFFFF"/>
+      </x:left>
+      <x:right/>
+      <x:top/>
+      <x:bottom style="thin">
+        <x:color rgb="FFCDD7E2"/>
+      </x:bottom>
+      <x:diagonal/>
+    </x:border>
+    <x:border>
+      <x:left/>
       <x:right/>
       <x:top/>
       <x:bottom style="thin">
@@ -153,7 +198,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="45">
+  <x:cellXfs count="56">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -220,67 +265,100 @@
     <x:xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="1" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="201" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="201" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="201" fontId="1" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="202" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="202" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="202" fontId="1" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="201" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="1" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="1" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="1" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="1" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="1" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="201" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="201" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="201" fontId="1" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="201" fontId="1" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="202" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="202" fontId="1" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="202" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="202" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="202" fontId="1" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="202" fontId="1" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -497,12 +575,13 @@
     <x:col min="7" max="7" width="25" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="25" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="28" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="26" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="28" hidden="0" customWidth="1"/>
     <x:col min="11" max="11" width="25" hidden="0" customWidth="1"/>
     <x:col min="12" max="12" width="30" hidden="0" customWidth="1"/>
     <x:col min="13" max="13" width="25" hidden="0" customWidth="1"/>
     <x:col min="14" max="14" width="25" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="45" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="30" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="45" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
@@ -523,10 +602,11 @@
       <x:c r="M1" s="6"/>
       <x:c r="N1" s="6"/>
       <x:c r="O1" s="6"/>
+      <x:c r="P1" s="6"/>
     </x:row>
     <x:row r="2" ht="27" customHeight="1">
       <x:c r="A2" s="7" t="str">
-        <x:v>第4列表頭請保留，第5列起填寫資料</x:v>
+        <x:v>第4列表頭、第5列中文說明請保留，第6列起填寫資料</x:v>
       </x:c>
       <x:c r="B2" s="3"/>
       <x:c r="C2" s="3"/>
@@ -542,6 +622,7 @@
       <x:c r="M2" s="3"/>
       <x:c r="N2" s="3"/>
       <x:c r="O2" s="3"/>
+      <x:c r="P2" s="3"/>
     </x:row>
     <x:row r="3" ht="10" customHeight="1">
       <x:c r="A3" s="1"/>
@@ -559,6 +640,7 @@
       <x:c r="M3" s="1"/>
       <x:c r="N3" s="1"/>
       <x:c r="O3" s="1"/>
+      <x:c r="P3" s="1"/>
     </x:row>
     <x:row r="4" ht="42" customHeight="1">
       <x:c r="A4" s="21" t="str">
@@ -603,519 +685,602 @@
       <x:c r="N4" s="22" t="str">
         <x:v>PCB_Footprint</x:v>
       </x:c>
-      <x:c r="O4" s="23" t="str">
+      <x:c r="O4" s="22" t="str">
+        <x:v>phase out</x:v>
+      </x:c>
+      <x:c r="P4" s="23" t="str">
         <x:v>零件狀態</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="24" customHeight="1">
-      <x:c r="A5" s="39"/>
-      <x:c r="B5" s="30"/>
-      <x:c r="C5" s="42"/>
-      <x:c r="D5" s="30"/>
-      <x:c r="E5" s="30"/>
-      <x:c r="F5" s="30"/>
-      <x:c r="G5" s="30"/>
-      <x:c r="H5" s="30"/>
-      <x:c r="I5" s="30"/>
-      <x:c r="J5" s="30"/>
-      <x:c r="K5" s="30"/>
-      <x:c r="L5" s="30"/>
-      <x:c r="M5" s="30"/>
-      <x:c r="N5" s="30"/>
-      <x:c r="O5" s="30"/>
+    <x:row r="5" ht="52" customHeight="1">
+      <x:c r="A5" s="32" t="str">
+        <x:v>階層：0 系統／1 模組／2 料件</x:v>
+      </x:c>
+      <x:c r="B5" s="33" t="str">
+        <x:v>設計 BOM 的料件名稱</x:v>
+      </x:c>
+      <x:c r="C5" s="33" t="str">
+        <x:v>單一產品的用量</x:v>
+      </x:c>
+      <x:c r="D5" s="33" t="str">
+        <x:v>電路位號，例如 C101、R1</x:v>
+      </x:c>
+      <x:c r="E5" s="33" t="str">
+        <x:v>單一廠商的單一原廠料號（MPN）</x:v>
+      </x:c>
+      <x:c r="F5" s="33" t="str">
+        <x:v>該列 MPN 的製造商</x:v>
+      </x:c>
+      <x:c r="G5" s="33" t="str">
+        <x:v>供應／核准來源狀態，保留原文</x:v>
+      </x:c>
+      <x:c r="H5" s="33" t="str">
+        <x:v>可共用多個實體料的上層料號</x:v>
+      </x:c>
+      <x:c r="I5" s="33" t="str">
+        <x:v>已申請的單一廠商、單一 MPN 實體料號</x:v>
+      </x:c>
+      <x:c r="J5" s="33" t="str">
+        <x:v>是否已有實體料號但缺 Symbol（保留原文）</x:v>
+      </x:c>
+      <x:c r="K5" s="33" t="str">
+        <x:v>實體料號對應的公司料名</x:v>
+      </x:c>
+      <x:c r="L5" s="33" t="str">
+        <x:v>料件規格，保留原內容</x:v>
+      </x:c>
+      <x:c r="M5" s="33" t="str">
+        <x:v>原理圖符號名稱，不代表 Symbol 有無</x:v>
+      </x:c>
+      <x:c r="N5" s="33" t="str">
+        <x:v>PCB 封裝名稱</x:v>
+      </x:c>
+      <x:c r="O5" s="33" t="str">
+        <x:v>零件狀態（保留公司原文）</x:v>
+      </x:c>
+      <x:c r="P5" s="34" t="str">
+        <x:v>新設計使用限制；不明填待確認</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="24" customHeight="1">
-      <x:c r="A6" s="40"/>
-      <x:c r="B6" s="31"/>
-      <x:c r="C6" s="43"/>
-      <x:c r="D6" s="31"/>
-      <x:c r="E6" s="31"/>
-      <x:c r="F6" s="31"/>
-      <x:c r="G6" s="31"/>
-      <x:c r="H6" s="31"/>
-      <x:c r="I6" s="31"/>
-      <x:c r="J6" s="31"/>
-      <x:c r="K6" s="31"/>
-      <x:c r="L6" s="31"/>
-      <x:c r="M6" s="31"/>
-      <x:c r="N6" s="31"/>
-      <x:c r="O6" s="31"/>
+      <x:c r="A6" s="50"/>
+      <x:c r="B6" s="41"/>
+      <x:c r="C6" s="53"/>
+      <x:c r="D6" s="41"/>
+      <x:c r="E6" s="41"/>
+      <x:c r="F6" s="41"/>
+      <x:c r="G6" s="41"/>
+      <x:c r="H6" s="41"/>
+      <x:c r="I6" s="41"/>
+      <x:c r="J6" s="41"/>
+      <x:c r="K6" s="41"/>
+      <x:c r="L6" s="41"/>
+      <x:c r="M6" s="41"/>
+      <x:c r="N6" s="41"/>
+      <x:c r="O6" s="41"/>
+      <x:c r="P6" s="41"/>
     </x:row>
     <x:row r="7" ht="24" customHeight="1">
-      <x:c r="A7" s="40"/>
-      <x:c r="B7" s="31"/>
-      <x:c r="C7" s="43"/>
-      <x:c r="D7" s="31"/>
-      <x:c r="E7" s="31"/>
-      <x:c r="F7" s="31"/>
-      <x:c r="G7" s="31"/>
-      <x:c r="H7" s="31"/>
-      <x:c r="I7" s="31"/>
-      <x:c r="J7" s="31"/>
-      <x:c r="K7" s="31"/>
-      <x:c r="L7" s="31"/>
-      <x:c r="M7" s="31"/>
-      <x:c r="N7" s="31"/>
-      <x:c r="O7" s="31"/>
+      <x:c r="A7" s="51"/>
+      <x:c r="B7" s="42"/>
+      <x:c r="C7" s="54"/>
+      <x:c r="D7" s="42"/>
+      <x:c r="E7" s="42"/>
+      <x:c r="F7" s="42"/>
+      <x:c r="G7" s="42"/>
+      <x:c r="H7" s="42"/>
+      <x:c r="I7" s="42"/>
+      <x:c r="J7" s="42"/>
+      <x:c r="K7" s="42"/>
+      <x:c r="L7" s="42"/>
+      <x:c r="M7" s="42"/>
+      <x:c r="N7" s="42"/>
+      <x:c r="O7" s="42"/>
+      <x:c r="P7" s="42"/>
     </x:row>
     <x:row r="8" ht="24" customHeight="1">
-      <x:c r="A8" s="40"/>
-      <x:c r="B8" s="31"/>
-      <x:c r="C8" s="43"/>
-      <x:c r="D8" s="31"/>
-      <x:c r="E8" s="31"/>
-      <x:c r="F8" s="31"/>
-      <x:c r="G8" s="31"/>
-      <x:c r="H8" s="31"/>
-      <x:c r="I8" s="31"/>
-      <x:c r="J8" s="31"/>
-      <x:c r="K8" s="31"/>
-      <x:c r="L8" s="31"/>
-      <x:c r="M8" s="31"/>
-      <x:c r="N8" s="31"/>
-      <x:c r="O8" s="31"/>
+      <x:c r="A8" s="51"/>
+      <x:c r="B8" s="42"/>
+      <x:c r="C8" s="54"/>
+      <x:c r="D8" s="42"/>
+      <x:c r="E8" s="42"/>
+      <x:c r="F8" s="42"/>
+      <x:c r="G8" s="42"/>
+      <x:c r="H8" s="42"/>
+      <x:c r="I8" s="42"/>
+      <x:c r="J8" s="42"/>
+      <x:c r="K8" s="42"/>
+      <x:c r="L8" s="42"/>
+      <x:c r="M8" s="42"/>
+      <x:c r="N8" s="42"/>
+      <x:c r="O8" s="42"/>
+      <x:c r="P8" s="42"/>
     </x:row>
     <x:row r="9" ht="24" customHeight="1">
-      <x:c r="A9" s="40"/>
-      <x:c r="B9" s="31"/>
-      <x:c r="C9" s="43"/>
-      <x:c r="D9" s="31"/>
-      <x:c r="E9" s="31"/>
-      <x:c r="F9" s="31"/>
-      <x:c r="G9" s="31"/>
-      <x:c r="H9" s="31"/>
-      <x:c r="I9" s="31"/>
-      <x:c r="J9" s="31"/>
-      <x:c r="K9" s="31"/>
-      <x:c r="L9" s="31"/>
-      <x:c r="M9" s="31"/>
-      <x:c r="N9" s="31"/>
-      <x:c r="O9" s="31"/>
+      <x:c r="A9" s="51"/>
+      <x:c r="B9" s="42"/>
+      <x:c r="C9" s="54"/>
+      <x:c r="D9" s="42"/>
+      <x:c r="E9" s="42"/>
+      <x:c r="F9" s="42"/>
+      <x:c r="G9" s="42"/>
+      <x:c r="H9" s="42"/>
+      <x:c r="I9" s="42"/>
+      <x:c r="J9" s="42"/>
+      <x:c r="K9" s="42"/>
+      <x:c r="L9" s="42"/>
+      <x:c r="M9" s="42"/>
+      <x:c r="N9" s="42"/>
+      <x:c r="O9" s="42"/>
+      <x:c r="P9" s="42"/>
     </x:row>
     <x:row r="10" ht="24" customHeight="1">
-      <x:c r="A10" s="40"/>
-      <x:c r="B10" s="31"/>
-      <x:c r="C10" s="43"/>
-      <x:c r="D10" s="31"/>
-      <x:c r="E10" s="31"/>
-      <x:c r="F10" s="31"/>
-      <x:c r="G10" s="31"/>
-      <x:c r="H10" s="31"/>
-      <x:c r="I10" s="31"/>
-      <x:c r="J10" s="31"/>
-      <x:c r="K10" s="31"/>
-      <x:c r="L10" s="31"/>
-      <x:c r="M10" s="31"/>
-      <x:c r="N10" s="31"/>
-      <x:c r="O10" s="31"/>
+      <x:c r="A10" s="51"/>
+      <x:c r="B10" s="42"/>
+      <x:c r="C10" s="54"/>
+      <x:c r="D10" s="42"/>
+      <x:c r="E10" s="42"/>
+      <x:c r="F10" s="42"/>
+      <x:c r="G10" s="42"/>
+      <x:c r="H10" s="42"/>
+      <x:c r="I10" s="42"/>
+      <x:c r="J10" s="42"/>
+      <x:c r="K10" s="42"/>
+      <x:c r="L10" s="42"/>
+      <x:c r="M10" s="42"/>
+      <x:c r="N10" s="42"/>
+      <x:c r="O10" s="42"/>
+      <x:c r="P10" s="42"/>
     </x:row>
     <x:row r="11" ht="24" customHeight="1">
-      <x:c r="A11" s="40"/>
-      <x:c r="B11" s="31"/>
-      <x:c r="C11" s="43"/>
-      <x:c r="D11" s="31"/>
-      <x:c r="E11" s="31"/>
-      <x:c r="F11" s="31"/>
-      <x:c r="G11" s="31"/>
-      <x:c r="H11" s="31"/>
-      <x:c r="I11" s="31"/>
-      <x:c r="J11" s="31"/>
-      <x:c r="K11" s="31"/>
-      <x:c r="L11" s="31"/>
-      <x:c r="M11" s="31"/>
-      <x:c r="N11" s="31"/>
-      <x:c r="O11" s="31"/>
+      <x:c r="A11" s="51"/>
+      <x:c r="B11" s="42"/>
+      <x:c r="C11" s="54"/>
+      <x:c r="D11" s="42"/>
+      <x:c r="E11" s="42"/>
+      <x:c r="F11" s="42"/>
+      <x:c r="G11" s="42"/>
+      <x:c r="H11" s="42"/>
+      <x:c r="I11" s="42"/>
+      <x:c r="J11" s="42"/>
+      <x:c r="K11" s="42"/>
+      <x:c r="L11" s="42"/>
+      <x:c r="M11" s="42"/>
+      <x:c r="N11" s="42"/>
+      <x:c r="O11" s="42"/>
+      <x:c r="P11" s="42"/>
     </x:row>
     <x:row r="12" ht="24" customHeight="1">
-      <x:c r="A12" s="40"/>
-      <x:c r="B12" s="31"/>
-      <x:c r="C12" s="43"/>
-      <x:c r="D12" s="31"/>
-      <x:c r="E12" s="31"/>
-      <x:c r="F12" s="31"/>
-      <x:c r="G12" s="31"/>
-      <x:c r="H12" s="31"/>
-      <x:c r="I12" s="31"/>
-      <x:c r="J12" s="31"/>
-      <x:c r="K12" s="31"/>
-      <x:c r="L12" s="31"/>
-      <x:c r="M12" s="31"/>
-      <x:c r="N12" s="31"/>
-      <x:c r="O12" s="31"/>
+      <x:c r="A12" s="51"/>
+      <x:c r="B12" s="42"/>
+      <x:c r="C12" s="54"/>
+      <x:c r="D12" s="42"/>
+      <x:c r="E12" s="42"/>
+      <x:c r="F12" s="42"/>
+      <x:c r="G12" s="42"/>
+      <x:c r="H12" s="42"/>
+      <x:c r="I12" s="42"/>
+      <x:c r="J12" s="42"/>
+      <x:c r="K12" s="42"/>
+      <x:c r="L12" s="42"/>
+      <x:c r="M12" s="42"/>
+      <x:c r="N12" s="42"/>
+      <x:c r="O12" s="42"/>
+      <x:c r="P12" s="42"/>
     </x:row>
     <x:row r="13" ht="24" customHeight="1">
-      <x:c r="A13" s="40"/>
-      <x:c r="B13" s="31"/>
-      <x:c r="C13" s="43"/>
-      <x:c r="D13" s="31"/>
-      <x:c r="E13" s="31"/>
-      <x:c r="F13" s="31"/>
-      <x:c r="G13" s="31"/>
-      <x:c r="H13" s="31"/>
-      <x:c r="I13" s="31"/>
-      <x:c r="J13" s="31"/>
-      <x:c r="K13" s="31"/>
-      <x:c r="L13" s="31"/>
-      <x:c r="M13" s="31"/>
-      <x:c r="N13" s="31"/>
-      <x:c r="O13" s="31"/>
+      <x:c r="A13" s="51"/>
+      <x:c r="B13" s="42"/>
+      <x:c r="C13" s="54"/>
+      <x:c r="D13" s="42"/>
+      <x:c r="E13" s="42"/>
+      <x:c r="F13" s="42"/>
+      <x:c r="G13" s="42"/>
+      <x:c r="H13" s="42"/>
+      <x:c r="I13" s="42"/>
+      <x:c r="J13" s="42"/>
+      <x:c r="K13" s="42"/>
+      <x:c r="L13" s="42"/>
+      <x:c r="M13" s="42"/>
+      <x:c r="N13" s="42"/>
+      <x:c r="O13" s="42"/>
+      <x:c r="P13" s="42"/>
     </x:row>
     <x:row r="14" ht="24" customHeight="1">
-      <x:c r="A14" s="40"/>
-      <x:c r="B14" s="31"/>
-      <x:c r="C14" s="43"/>
-      <x:c r="D14" s="31"/>
-      <x:c r="E14" s="31"/>
-      <x:c r="F14" s="31"/>
-      <x:c r="G14" s="31"/>
-      <x:c r="H14" s="31"/>
-      <x:c r="I14" s="31"/>
-      <x:c r="J14" s="31"/>
-      <x:c r="K14" s="31"/>
-      <x:c r="L14" s="31"/>
-      <x:c r="M14" s="31"/>
-      <x:c r="N14" s="31"/>
-      <x:c r="O14" s="31"/>
+      <x:c r="A14" s="51"/>
+      <x:c r="B14" s="42"/>
+      <x:c r="C14" s="54"/>
+      <x:c r="D14" s="42"/>
+      <x:c r="E14" s="42"/>
+      <x:c r="F14" s="42"/>
+      <x:c r="G14" s="42"/>
+      <x:c r="H14" s="42"/>
+      <x:c r="I14" s="42"/>
+      <x:c r="J14" s="42"/>
+      <x:c r="K14" s="42"/>
+      <x:c r="L14" s="42"/>
+      <x:c r="M14" s="42"/>
+      <x:c r="N14" s="42"/>
+      <x:c r="O14" s="42"/>
+      <x:c r="P14" s="42"/>
     </x:row>
     <x:row r="15" ht="24" customHeight="1">
-      <x:c r="A15" s="40"/>
-      <x:c r="B15" s="31"/>
-      <x:c r="C15" s="43"/>
-      <x:c r="D15" s="31"/>
-      <x:c r="E15" s="31"/>
-      <x:c r="F15" s="31"/>
-      <x:c r="G15" s="31"/>
-      <x:c r="H15" s="31"/>
-      <x:c r="I15" s="31"/>
-      <x:c r="J15" s="31"/>
-      <x:c r="K15" s="31"/>
-      <x:c r="L15" s="31"/>
-      <x:c r="M15" s="31"/>
-      <x:c r="N15" s="31"/>
-      <x:c r="O15" s="31"/>
+      <x:c r="A15" s="51"/>
+      <x:c r="B15" s="42"/>
+      <x:c r="C15" s="54"/>
+      <x:c r="D15" s="42"/>
+      <x:c r="E15" s="42"/>
+      <x:c r="F15" s="42"/>
+      <x:c r="G15" s="42"/>
+      <x:c r="H15" s="42"/>
+      <x:c r="I15" s="42"/>
+      <x:c r="J15" s="42"/>
+      <x:c r="K15" s="42"/>
+      <x:c r="L15" s="42"/>
+      <x:c r="M15" s="42"/>
+      <x:c r="N15" s="42"/>
+      <x:c r="O15" s="42"/>
+      <x:c r="P15" s="42"/>
     </x:row>
     <x:row r="16" ht="24" customHeight="1">
-      <x:c r="A16" s="40"/>
-      <x:c r="B16" s="31"/>
-      <x:c r="C16" s="43"/>
-      <x:c r="D16" s="31"/>
-      <x:c r="E16" s="31"/>
-      <x:c r="F16" s="31"/>
-      <x:c r="G16" s="31"/>
-      <x:c r="H16" s="31"/>
-      <x:c r="I16" s="31"/>
-      <x:c r="J16" s="31"/>
-      <x:c r="K16" s="31"/>
-      <x:c r="L16" s="31"/>
-      <x:c r="M16" s="31"/>
-      <x:c r="N16" s="31"/>
-      <x:c r="O16" s="31"/>
+      <x:c r="A16" s="51"/>
+      <x:c r="B16" s="42"/>
+      <x:c r="C16" s="54"/>
+      <x:c r="D16" s="42"/>
+      <x:c r="E16" s="42"/>
+      <x:c r="F16" s="42"/>
+      <x:c r="G16" s="42"/>
+      <x:c r="H16" s="42"/>
+      <x:c r="I16" s="42"/>
+      <x:c r="J16" s="42"/>
+      <x:c r="K16" s="42"/>
+      <x:c r="L16" s="42"/>
+      <x:c r="M16" s="42"/>
+      <x:c r="N16" s="42"/>
+      <x:c r="O16" s="42"/>
+      <x:c r="P16" s="42"/>
     </x:row>
     <x:row r="17" ht="24" customHeight="1">
-      <x:c r="A17" s="40"/>
-      <x:c r="B17" s="31"/>
-      <x:c r="C17" s="43"/>
-      <x:c r="D17" s="31"/>
-      <x:c r="E17" s="31"/>
-      <x:c r="F17" s="31"/>
-      <x:c r="G17" s="31"/>
-      <x:c r="H17" s="31"/>
-      <x:c r="I17" s="31"/>
-      <x:c r="J17" s="31"/>
-      <x:c r="K17" s="31"/>
-      <x:c r="L17" s="31"/>
-      <x:c r="M17" s="31"/>
-      <x:c r="N17" s="31"/>
-      <x:c r="O17" s="31"/>
+      <x:c r="A17" s="51"/>
+      <x:c r="B17" s="42"/>
+      <x:c r="C17" s="54"/>
+      <x:c r="D17" s="42"/>
+      <x:c r="E17" s="42"/>
+      <x:c r="F17" s="42"/>
+      <x:c r="G17" s="42"/>
+      <x:c r="H17" s="42"/>
+      <x:c r="I17" s="42"/>
+      <x:c r="J17" s="42"/>
+      <x:c r="K17" s="42"/>
+      <x:c r="L17" s="42"/>
+      <x:c r="M17" s="42"/>
+      <x:c r="N17" s="42"/>
+      <x:c r="O17" s="42"/>
+      <x:c r="P17" s="42"/>
     </x:row>
     <x:row r="18" ht="24" customHeight="1">
-      <x:c r="A18" s="40"/>
-      <x:c r="B18" s="31"/>
-      <x:c r="C18" s="43"/>
-      <x:c r="D18" s="31"/>
-      <x:c r="E18" s="31"/>
-      <x:c r="F18" s="31"/>
-      <x:c r="G18" s="31"/>
-      <x:c r="H18" s="31"/>
-      <x:c r="I18" s="31"/>
-      <x:c r="J18" s="31"/>
-      <x:c r="K18" s="31"/>
-      <x:c r="L18" s="31"/>
-      <x:c r="M18" s="31"/>
-      <x:c r="N18" s="31"/>
-      <x:c r="O18" s="31"/>
+      <x:c r="A18" s="51"/>
+      <x:c r="B18" s="42"/>
+      <x:c r="C18" s="54"/>
+      <x:c r="D18" s="42"/>
+      <x:c r="E18" s="42"/>
+      <x:c r="F18" s="42"/>
+      <x:c r="G18" s="42"/>
+      <x:c r="H18" s="42"/>
+      <x:c r="I18" s="42"/>
+      <x:c r="J18" s="42"/>
+      <x:c r="K18" s="42"/>
+      <x:c r="L18" s="42"/>
+      <x:c r="M18" s="42"/>
+      <x:c r="N18" s="42"/>
+      <x:c r="O18" s="42"/>
+      <x:c r="P18" s="42"/>
     </x:row>
     <x:row r="19" ht="24" customHeight="1">
-      <x:c r="A19" s="40"/>
-      <x:c r="B19" s="31"/>
-      <x:c r="C19" s="43"/>
-      <x:c r="D19" s="31"/>
-      <x:c r="E19" s="31"/>
-      <x:c r="F19" s="31"/>
-      <x:c r="G19" s="31"/>
-      <x:c r="H19" s="31"/>
-      <x:c r="I19" s="31"/>
-      <x:c r="J19" s="31"/>
-      <x:c r="K19" s="31"/>
-      <x:c r="L19" s="31"/>
-      <x:c r="M19" s="31"/>
-      <x:c r="N19" s="31"/>
-      <x:c r="O19" s="31"/>
+      <x:c r="A19" s="51"/>
+      <x:c r="B19" s="42"/>
+      <x:c r="C19" s="54"/>
+      <x:c r="D19" s="42"/>
+      <x:c r="E19" s="42"/>
+      <x:c r="F19" s="42"/>
+      <x:c r="G19" s="42"/>
+      <x:c r="H19" s="42"/>
+      <x:c r="I19" s="42"/>
+      <x:c r="J19" s="42"/>
+      <x:c r="K19" s="42"/>
+      <x:c r="L19" s="42"/>
+      <x:c r="M19" s="42"/>
+      <x:c r="N19" s="42"/>
+      <x:c r="O19" s="42"/>
+      <x:c r="P19" s="42"/>
     </x:row>
     <x:row r="20" ht="24" customHeight="1">
-      <x:c r="A20" s="40"/>
-      <x:c r="B20" s="31"/>
-      <x:c r="C20" s="43"/>
-      <x:c r="D20" s="31"/>
-      <x:c r="E20" s="31"/>
-      <x:c r="F20" s="31"/>
-      <x:c r="G20" s="31"/>
-      <x:c r="H20" s="31"/>
-      <x:c r="I20" s="31"/>
-      <x:c r="J20" s="31"/>
-      <x:c r="K20" s="31"/>
-      <x:c r="L20" s="31"/>
-      <x:c r="M20" s="31"/>
-      <x:c r="N20" s="31"/>
-      <x:c r="O20" s="31"/>
+      <x:c r="A20" s="51"/>
+      <x:c r="B20" s="42"/>
+      <x:c r="C20" s="54"/>
+      <x:c r="D20" s="42"/>
+      <x:c r="E20" s="42"/>
+      <x:c r="F20" s="42"/>
+      <x:c r="G20" s="42"/>
+      <x:c r="H20" s="42"/>
+      <x:c r="I20" s="42"/>
+      <x:c r="J20" s="42"/>
+      <x:c r="K20" s="42"/>
+      <x:c r="L20" s="42"/>
+      <x:c r="M20" s="42"/>
+      <x:c r="N20" s="42"/>
+      <x:c r="O20" s="42"/>
+      <x:c r="P20" s="42"/>
     </x:row>
     <x:row r="21" ht="24" customHeight="1">
-      <x:c r="A21" s="40"/>
-      <x:c r="B21" s="31"/>
-      <x:c r="C21" s="43"/>
-      <x:c r="D21" s="31"/>
-      <x:c r="E21" s="31"/>
-      <x:c r="F21" s="31"/>
-      <x:c r="G21" s="31"/>
-      <x:c r="H21" s="31"/>
-      <x:c r="I21" s="31"/>
-      <x:c r="J21" s="31"/>
-      <x:c r="K21" s="31"/>
-      <x:c r="L21" s="31"/>
-      <x:c r="M21" s="31"/>
-      <x:c r="N21" s="31"/>
-      <x:c r="O21" s="31"/>
+      <x:c r="A21" s="51"/>
+      <x:c r="B21" s="42"/>
+      <x:c r="C21" s="54"/>
+      <x:c r="D21" s="42"/>
+      <x:c r="E21" s="42"/>
+      <x:c r="F21" s="42"/>
+      <x:c r="G21" s="42"/>
+      <x:c r="H21" s="42"/>
+      <x:c r="I21" s="42"/>
+      <x:c r="J21" s="42"/>
+      <x:c r="K21" s="42"/>
+      <x:c r="L21" s="42"/>
+      <x:c r="M21" s="42"/>
+      <x:c r="N21" s="42"/>
+      <x:c r="O21" s="42"/>
+      <x:c r="P21" s="42"/>
     </x:row>
     <x:row r="22" ht="24" customHeight="1">
-      <x:c r="A22" s="40"/>
-      <x:c r="B22" s="31"/>
-      <x:c r="C22" s="43"/>
-      <x:c r="D22" s="31"/>
-      <x:c r="E22" s="31"/>
-      <x:c r="F22" s="31"/>
-      <x:c r="G22" s="31"/>
-      <x:c r="H22" s="31"/>
-      <x:c r="I22" s="31"/>
-      <x:c r="J22" s="31"/>
-      <x:c r="K22" s="31"/>
-      <x:c r="L22" s="31"/>
-      <x:c r="M22" s="31"/>
-      <x:c r="N22" s="31"/>
-      <x:c r="O22" s="31"/>
+      <x:c r="A22" s="51"/>
+      <x:c r="B22" s="42"/>
+      <x:c r="C22" s="54"/>
+      <x:c r="D22" s="42"/>
+      <x:c r="E22" s="42"/>
+      <x:c r="F22" s="42"/>
+      <x:c r="G22" s="42"/>
+      <x:c r="H22" s="42"/>
+      <x:c r="I22" s="42"/>
+      <x:c r="J22" s="42"/>
+      <x:c r="K22" s="42"/>
+      <x:c r="L22" s="42"/>
+      <x:c r="M22" s="42"/>
+      <x:c r="N22" s="42"/>
+      <x:c r="O22" s="42"/>
+      <x:c r="P22" s="42"/>
     </x:row>
     <x:row r="23" ht="24" customHeight="1">
-      <x:c r="A23" s="40"/>
-      <x:c r="B23" s="31"/>
-      <x:c r="C23" s="43"/>
-      <x:c r="D23" s="31"/>
-      <x:c r="E23" s="31"/>
-      <x:c r="F23" s="31"/>
-      <x:c r="G23" s="31"/>
-      <x:c r="H23" s="31"/>
-      <x:c r="I23" s="31"/>
-      <x:c r="J23" s="31"/>
-      <x:c r="K23" s="31"/>
-      <x:c r="L23" s="31"/>
-      <x:c r="M23" s="31"/>
-      <x:c r="N23" s="31"/>
-      <x:c r="O23" s="31"/>
+      <x:c r="A23" s="51"/>
+      <x:c r="B23" s="42"/>
+      <x:c r="C23" s="54"/>
+      <x:c r="D23" s="42"/>
+      <x:c r="E23" s="42"/>
+      <x:c r="F23" s="42"/>
+      <x:c r="G23" s="42"/>
+      <x:c r="H23" s="42"/>
+      <x:c r="I23" s="42"/>
+      <x:c r="J23" s="42"/>
+      <x:c r="K23" s="42"/>
+      <x:c r="L23" s="42"/>
+      <x:c r="M23" s="42"/>
+      <x:c r="N23" s="42"/>
+      <x:c r="O23" s="42"/>
+      <x:c r="P23" s="42"/>
     </x:row>
     <x:row r="24" ht="24" customHeight="1">
-      <x:c r="A24" s="40"/>
-      <x:c r="B24" s="31"/>
-      <x:c r="C24" s="43"/>
-      <x:c r="D24" s="31"/>
-      <x:c r="E24" s="31"/>
-      <x:c r="F24" s="31"/>
-      <x:c r="G24" s="31"/>
-      <x:c r="H24" s="31"/>
-      <x:c r="I24" s="31"/>
-      <x:c r="J24" s="31"/>
-      <x:c r="K24" s="31"/>
-      <x:c r="L24" s="31"/>
-      <x:c r="M24" s="31"/>
-      <x:c r="N24" s="31"/>
-      <x:c r="O24" s="31"/>
+      <x:c r="A24" s="51"/>
+      <x:c r="B24" s="42"/>
+      <x:c r="C24" s="54"/>
+      <x:c r="D24" s="42"/>
+      <x:c r="E24" s="42"/>
+      <x:c r="F24" s="42"/>
+      <x:c r="G24" s="42"/>
+      <x:c r="H24" s="42"/>
+      <x:c r="I24" s="42"/>
+      <x:c r="J24" s="42"/>
+      <x:c r="K24" s="42"/>
+      <x:c r="L24" s="42"/>
+      <x:c r="M24" s="42"/>
+      <x:c r="N24" s="42"/>
+      <x:c r="O24" s="42"/>
+      <x:c r="P24" s="42"/>
     </x:row>
     <x:row r="25" ht="24" customHeight="1">
-      <x:c r="A25" s="40"/>
-      <x:c r="B25" s="31"/>
-      <x:c r="C25" s="43"/>
-      <x:c r="D25" s="31"/>
-      <x:c r="E25" s="31"/>
-      <x:c r="F25" s="31"/>
-      <x:c r="G25" s="31"/>
-      <x:c r="H25" s="31"/>
-      <x:c r="I25" s="31"/>
-      <x:c r="J25" s="31"/>
-      <x:c r="K25" s="31"/>
-      <x:c r="L25" s="31"/>
-      <x:c r="M25" s="31"/>
-      <x:c r="N25" s="31"/>
-      <x:c r="O25" s="31"/>
+      <x:c r="A25" s="51"/>
+      <x:c r="B25" s="42"/>
+      <x:c r="C25" s="54"/>
+      <x:c r="D25" s="42"/>
+      <x:c r="E25" s="42"/>
+      <x:c r="F25" s="42"/>
+      <x:c r="G25" s="42"/>
+      <x:c r="H25" s="42"/>
+      <x:c r="I25" s="42"/>
+      <x:c r="J25" s="42"/>
+      <x:c r="K25" s="42"/>
+      <x:c r="L25" s="42"/>
+      <x:c r="M25" s="42"/>
+      <x:c r="N25" s="42"/>
+      <x:c r="O25" s="42"/>
+      <x:c r="P25" s="42"/>
     </x:row>
     <x:row r="26" ht="24" customHeight="1">
-      <x:c r="A26" s="40"/>
-      <x:c r="B26" s="31"/>
-      <x:c r="C26" s="43"/>
-      <x:c r="D26" s="31"/>
-      <x:c r="E26" s="31"/>
-      <x:c r="F26" s="31"/>
-      <x:c r="G26" s="31"/>
-      <x:c r="H26" s="31"/>
-      <x:c r="I26" s="31"/>
-      <x:c r="J26" s="31"/>
-      <x:c r="K26" s="31"/>
-      <x:c r="L26" s="31"/>
-      <x:c r="M26" s="31"/>
-      <x:c r="N26" s="31"/>
-      <x:c r="O26" s="31"/>
+      <x:c r="A26" s="51"/>
+      <x:c r="B26" s="42"/>
+      <x:c r="C26" s="54"/>
+      <x:c r="D26" s="42"/>
+      <x:c r="E26" s="42"/>
+      <x:c r="F26" s="42"/>
+      <x:c r="G26" s="42"/>
+      <x:c r="H26" s="42"/>
+      <x:c r="I26" s="42"/>
+      <x:c r="J26" s="42"/>
+      <x:c r="K26" s="42"/>
+      <x:c r="L26" s="42"/>
+      <x:c r="M26" s="42"/>
+      <x:c r="N26" s="42"/>
+      <x:c r="O26" s="42"/>
+      <x:c r="P26" s="42"/>
     </x:row>
     <x:row r="27" ht="24" customHeight="1">
-      <x:c r="A27" s="40"/>
-      <x:c r="B27" s="31"/>
-      <x:c r="C27" s="43"/>
-      <x:c r="D27" s="31"/>
-      <x:c r="E27" s="31"/>
-      <x:c r="F27" s="31"/>
-      <x:c r="G27" s="31"/>
-      <x:c r="H27" s="31"/>
-      <x:c r="I27" s="31"/>
-      <x:c r="J27" s="31"/>
-      <x:c r="K27" s="31"/>
-      <x:c r="L27" s="31"/>
-      <x:c r="M27" s="31"/>
-      <x:c r="N27" s="31"/>
-      <x:c r="O27" s="31"/>
+      <x:c r="A27" s="51"/>
+      <x:c r="B27" s="42"/>
+      <x:c r="C27" s="54"/>
+      <x:c r="D27" s="42"/>
+      <x:c r="E27" s="42"/>
+      <x:c r="F27" s="42"/>
+      <x:c r="G27" s="42"/>
+      <x:c r="H27" s="42"/>
+      <x:c r="I27" s="42"/>
+      <x:c r="J27" s="42"/>
+      <x:c r="K27" s="42"/>
+      <x:c r="L27" s="42"/>
+      <x:c r="M27" s="42"/>
+      <x:c r="N27" s="42"/>
+      <x:c r="O27" s="42"/>
+      <x:c r="P27" s="42"/>
     </x:row>
     <x:row r="28" ht="24" customHeight="1">
-      <x:c r="A28" s="40"/>
-      <x:c r="B28" s="31"/>
-      <x:c r="C28" s="43"/>
-      <x:c r="D28" s="31"/>
-      <x:c r="E28" s="31"/>
-      <x:c r="F28" s="31"/>
-      <x:c r="G28" s="31"/>
-      <x:c r="H28" s="31"/>
-      <x:c r="I28" s="31"/>
-      <x:c r="J28" s="31"/>
-      <x:c r="K28" s="31"/>
-      <x:c r="L28" s="31"/>
-      <x:c r="M28" s="31"/>
-      <x:c r="N28" s="31"/>
-      <x:c r="O28" s="31"/>
+      <x:c r="A28" s="51"/>
+      <x:c r="B28" s="42"/>
+      <x:c r="C28" s="54"/>
+      <x:c r="D28" s="42"/>
+      <x:c r="E28" s="42"/>
+      <x:c r="F28" s="42"/>
+      <x:c r="G28" s="42"/>
+      <x:c r="H28" s="42"/>
+      <x:c r="I28" s="42"/>
+      <x:c r="J28" s="42"/>
+      <x:c r="K28" s="42"/>
+      <x:c r="L28" s="42"/>
+      <x:c r="M28" s="42"/>
+      <x:c r="N28" s="42"/>
+      <x:c r="O28" s="42"/>
+      <x:c r="P28" s="42"/>
     </x:row>
     <x:row r="29" ht="24" customHeight="1">
-      <x:c r="A29" s="40"/>
-      <x:c r="B29" s="31"/>
-      <x:c r="C29" s="43"/>
-      <x:c r="D29" s="31"/>
-      <x:c r="E29" s="31"/>
-      <x:c r="F29" s="31"/>
-      <x:c r="G29" s="31"/>
-      <x:c r="H29" s="31"/>
-      <x:c r="I29" s="31"/>
-      <x:c r="J29" s="31"/>
-      <x:c r="K29" s="31"/>
-      <x:c r="L29" s="31"/>
-      <x:c r="M29" s="31"/>
-      <x:c r="N29" s="31"/>
-      <x:c r="O29" s="31"/>
+      <x:c r="A29" s="51"/>
+      <x:c r="B29" s="42"/>
+      <x:c r="C29" s="54"/>
+      <x:c r="D29" s="42"/>
+      <x:c r="E29" s="42"/>
+      <x:c r="F29" s="42"/>
+      <x:c r="G29" s="42"/>
+      <x:c r="H29" s="42"/>
+      <x:c r="I29" s="42"/>
+      <x:c r="J29" s="42"/>
+      <x:c r="K29" s="42"/>
+      <x:c r="L29" s="42"/>
+      <x:c r="M29" s="42"/>
+      <x:c r="N29" s="42"/>
+      <x:c r="O29" s="42"/>
+      <x:c r="P29" s="42"/>
     </x:row>
     <x:row r="30" ht="24" customHeight="1">
-      <x:c r="A30" s="40"/>
-      <x:c r="B30" s="31"/>
-      <x:c r="C30" s="43"/>
-      <x:c r="D30" s="31"/>
-      <x:c r="E30" s="31"/>
-      <x:c r="F30" s="31"/>
-      <x:c r="G30" s="31"/>
-      <x:c r="H30" s="31"/>
-      <x:c r="I30" s="31"/>
-      <x:c r="J30" s="31"/>
-      <x:c r="K30" s="31"/>
-      <x:c r="L30" s="31"/>
-      <x:c r="M30" s="31"/>
-      <x:c r="N30" s="31"/>
-      <x:c r="O30" s="31"/>
+      <x:c r="A30" s="51"/>
+      <x:c r="B30" s="42"/>
+      <x:c r="C30" s="54"/>
+      <x:c r="D30" s="42"/>
+      <x:c r="E30" s="42"/>
+      <x:c r="F30" s="42"/>
+      <x:c r="G30" s="42"/>
+      <x:c r="H30" s="42"/>
+      <x:c r="I30" s="42"/>
+      <x:c r="J30" s="42"/>
+      <x:c r="K30" s="42"/>
+      <x:c r="L30" s="42"/>
+      <x:c r="M30" s="42"/>
+      <x:c r="N30" s="42"/>
+      <x:c r="O30" s="42"/>
+      <x:c r="P30" s="42"/>
     </x:row>
     <x:row r="31" ht="24" customHeight="1">
-      <x:c r="A31" s="40"/>
-      <x:c r="B31" s="31"/>
-      <x:c r="C31" s="43"/>
-      <x:c r="D31" s="31"/>
-      <x:c r="E31" s="31"/>
-      <x:c r="F31" s="31"/>
-      <x:c r="G31" s="31"/>
-      <x:c r="H31" s="31"/>
-      <x:c r="I31" s="31"/>
-      <x:c r="J31" s="31"/>
-      <x:c r="K31" s="31"/>
-      <x:c r="L31" s="31"/>
-      <x:c r="M31" s="31"/>
-      <x:c r="N31" s="31"/>
-      <x:c r="O31" s="31"/>
+      <x:c r="A31" s="51"/>
+      <x:c r="B31" s="42"/>
+      <x:c r="C31" s="54"/>
+      <x:c r="D31" s="42"/>
+      <x:c r="E31" s="42"/>
+      <x:c r="F31" s="42"/>
+      <x:c r="G31" s="42"/>
+      <x:c r="H31" s="42"/>
+      <x:c r="I31" s="42"/>
+      <x:c r="J31" s="42"/>
+      <x:c r="K31" s="42"/>
+      <x:c r="L31" s="42"/>
+      <x:c r="M31" s="42"/>
+      <x:c r="N31" s="42"/>
+      <x:c r="O31" s="42"/>
+      <x:c r="P31" s="42"/>
     </x:row>
     <x:row r="32" ht="24" customHeight="1">
-      <x:c r="A32" s="40"/>
-      <x:c r="B32" s="31"/>
-      <x:c r="C32" s="43"/>
-      <x:c r="D32" s="31"/>
-      <x:c r="E32" s="31"/>
-      <x:c r="F32" s="31"/>
-      <x:c r="G32" s="31"/>
-      <x:c r="H32" s="31"/>
-      <x:c r="I32" s="31"/>
-      <x:c r="J32" s="31"/>
-      <x:c r="K32" s="31"/>
-      <x:c r="L32" s="31"/>
-      <x:c r="M32" s="31"/>
-      <x:c r="N32" s="31"/>
-      <x:c r="O32" s="31"/>
+      <x:c r="A32" s="51"/>
+      <x:c r="B32" s="42"/>
+      <x:c r="C32" s="54"/>
+      <x:c r="D32" s="42"/>
+      <x:c r="E32" s="42"/>
+      <x:c r="F32" s="42"/>
+      <x:c r="G32" s="42"/>
+      <x:c r="H32" s="42"/>
+      <x:c r="I32" s="42"/>
+      <x:c r="J32" s="42"/>
+      <x:c r="K32" s="42"/>
+      <x:c r="L32" s="42"/>
+      <x:c r="M32" s="42"/>
+      <x:c r="N32" s="42"/>
+      <x:c r="O32" s="42"/>
+      <x:c r="P32" s="42"/>
     </x:row>
     <x:row r="33" ht="24" customHeight="1">
-      <x:c r="A33" s="40"/>
-      <x:c r="B33" s="31"/>
-      <x:c r="C33" s="43"/>
-      <x:c r="D33" s="31"/>
-      <x:c r="E33" s="31"/>
-      <x:c r="F33" s="31"/>
-      <x:c r="G33" s="31"/>
-      <x:c r="H33" s="31"/>
-      <x:c r="I33" s="31"/>
-      <x:c r="J33" s="31"/>
-      <x:c r="K33" s="31"/>
-      <x:c r="L33" s="31"/>
-      <x:c r="M33" s="31"/>
-      <x:c r="N33" s="31"/>
-      <x:c r="O33" s="31"/>
+      <x:c r="A33" s="51"/>
+      <x:c r="B33" s="42"/>
+      <x:c r="C33" s="54"/>
+      <x:c r="D33" s="42"/>
+      <x:c r="E33" s="42"/>
+      <x:c r="F33" s="42"/>
+      <x:c r="G33" s="42"/>
+      <x:c r="H33" s="42"/>
+      <x:c r="I33" s="42"/>
+      <x:c r="J33" s="42"/>
+      <x:c r="K33" s="42"/>
+      <x:c r="L33" s="42"/>
+      <x:c r="M33" s="42"/>
+      <x:c r="N33" s="42"/>
+      <x:c r="O33" s="42"/>
+      <x:c r="P33" s="42"/>
     </x:row>
     <x:row r="34" ht="24" customHeight="1">
-      <x:c r="A34" s="41"/>
-      <x:c r="B34" s="32"/>
-      <x:c r="C34" s="44"/>
-      <x:c r="D34" s="32"/>
-      <x:c r="E34" s="32"/>
-      <x:c r="F34" s="32"/>
-      <x:c r="G34" s="32"/>
-      <x:c r="H34" s="32"/>
-      <x:c r="I34" s="32"/>
-      <x:c r="J34" s="32"/>
-      <x:c r="K34" s="32"/>
-      <x:c r="L34" s="32"/>
-      <x:c r="M34" s="32"/>
-      <x:c r="N34" s="32"/>
-      <x:c r="O34" s="32"/>
+      <x:c r="A34" s="51"/>
+      <x:c r="B34" s="42"/>
+      <x:c r="C34" s="54"/>
+      <x:c r="D34" s="42"/>
+      <x:c r="E34" s="42"/>
+      <x:c r="F34" s="42"/>
+      <x:c r="G34" s="42"/>
+      <x:c r="H34" s="42"/>
+      <x:c r="I34" s="42"/>
+      <x:c r="J34" s="42"/>
+      <x:c r="K34" s="42"/>
+      <x:c r="L34" s="42"/>
+      <x:c r="M34" s="42"/>
+      <x:c r="N34" s="42"/>
+      <x:c r="O34" s="42"/>
+      <x:c r="P34" s="42"/>
+    </x:row>
+    <x:row r="35" ht="24" customHeight="1">
+      <x:c r="A35" s="52"/>
+      <x:c r="B35" s="43"/>
+      <x:c r="C35" s="55"/>
+      <x:c r="D35" s="43"/>
+      <x:c r="E35" s="43"/>
+      <x:c r="F35" s="43"/>
+      <x:c r="G35" s="43"/>
+      <x:c r="H35" s="43"/>
+      <x:c r="I35" s="43"/>
+      <x:c r="J35" s="43"/>
+      <x:c r="K35" s="43"/>
+      <x:c r="L35" s="43"/>
+      <x:c r="M35" s="43"/>
+      <x:c r="N35" s="43"/>
+      <x:c r="O35" s="43"/>
+      <x:c r="P35" s="43"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
